--- a/Manuscript Variant Workbooks/Grec17-to-Holmes94_MS-spreadsheet.xlsx
+++ b/Manuscript Variant Workbooks/Grec17-to-Holmes94_MS-spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/8 Corrections/Files to Upload/To Github/Manuscript Variant Workbooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/186593bc330ab858/Cambridge PhD/Thesis/10 The Final Final Version/New and Updated Files for Upload/MS Variant Spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="632" documentId="8_{EF385ACB-72A7-4E04-8977-FA4FC6A9FEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C7A2156-BB49-4815-A86F-314C54FE41FC}"/>
+  <xr:revisionPtr revIDLastSave="717" documentId="8_{EF385ACB-72A7-4E04-8977-FA4FC6A9FEBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327DF2D1-4039-44A6-8A2A-B2E37F53A4E7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5BB4D106-A247-41F8-A104-83D51E35EC09}"/>
   </bookViews>
@@ -32,8 +32,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">AddOmits!$A$1:$AE$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gen-filters'!$A$1:$AE$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Harmonization!$A$1:$AE$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gen-filters'!$A$1:$AE$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Harmonization!$A$1:$AF$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unfiltered Data'!$A$1:$AH$252</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">WF_AO_LM!$A$1:$AE$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">WF_SUB!$A$1:$AH$15</definedName>
@@ -2772,6 +2772,15 @@
     <author>tc={2E137862-4F64-4708-9E15-347B1D3C02B6}</author>
     <author>tc={8815700D-36AA-4FB8-AF8E-41A4B7606096}</author>
     <author>tc={ABD68C27-D4A9-44EE-AF6F-3CB8BDA6A138}</author>
+    <author>tc={F871D504-E335-4464-BC26-F968C341E623}</author>
+    <author>tc={B7BC671D-705C-4D5C-B912-A3612A768BDC}</author>
+    <author>tc={F677BA5A-9EB4-4E49-B10C-8863788FBC2A}</author>
+    <author>tc={4A07708A-FC38-41EF-A05C-7D7649D41200}</author>
+    <author>tc={0AB730C8-C4B5-42EB-BB13-7117616499F2}</author>
+    <author>tc={A6EB124F-E722-4A46-855B-1045507D0D74}</author>
+    <author>tc={12F049EC-7824-407C-8639-62FB5D5BDF75}</author>
+    <author>tc={6765579E-3E10-490D-89EC-59DA74345D48}</author>
+    <author>tc={52E5C178-4B24-4FDF-9343-87C45F414C4B}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{72F44AF7-7BFB-488E-B07E-F358911F6795}">
@@ -3177,7 +3186,7 @@
     For substitutions, the word frequency of the autograph reading</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{414DC294-8443-45CC-BD5F-14C7B29518D3}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{414DC294-8443-45CC-BD5F-14C7B29518D3}">
       <text>
         <r>
           <rPr>
@@ -3201,7 +3210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{62D859CE-680C-4E4D-A59F-BD0C0AB09BA5}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{62D859CE-680C-4E4D-A59F-BD0C0AB09BA5}">
       <text>
         <r>
           <rPr>
@@ -3225,7 +3234,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{EF39C85E-CA19-48FE-A057-DF2EFD8F83A7}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{EF39C85E-CA19-48FE-A057-DF2EFD8F83A7}">
       <text>
         <r>
           <rPr>
@@ -3249,7 +3258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{72CEC05B-BEA6-4260-9B80-F3504C7820BA}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{72CEC05B-BEA6-4260-9B80-F3504C7820BA}">
       <text>
         <r>
           <rPr>
@@ -3273,7 +3282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{D8748D2F-1989-4587-8224-553466610D5B}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{D8748D2F-1989-4587-8224-553466610D5B}">
       <text>
         <r>
           <rPr>
@@ -3298,7 +3307,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{CD3BCD97-D55A-4CA4-BA45-DB9937235FD0}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{CD3BCD97-D55A-4CA4-BA45-DB9937235FD0}">
       <text>
         <r>
           <rPr>
@@ -3322,7 +3331,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{331E0090-6277-44E4-BEF3-9DB529862FD8}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{331E0090-6277-44E4-BEF3-9DB529862FD8}">
       <text>
         <r>
           <rPr>
@@ -3346,7 +3355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="3" shapeId="0" xr:uid="{2E137862-4F64-4708-9E15-347B1D3C02B6}">
+    <comment ref="D11" authorId="3" shapeId="0" xr:uid="{2E137862-4F64-4708-9E15-347B1D3C02B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3354,7 +3363,7 @@
     The number of variants that harmonized to parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D14" authorId="4" shapeId="0" xr:uid="{8815700D-36AA-4FB8-AF8E-41A4B7606096}">
+    <comment ref="D12" authorId="4" shapeId="0" xr:uid="{8815700D-36AA-4FB8-AF8E-41A4B7606096}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3362,7 +3371,79 @@
     The number of variants that disharmonized from  parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D15" authorId="5" shapeId="0" xr:uid="{ABD68C27-D4A9-44EE-AF6F-3CB8BDA6A138}">
+    <comment ref="D13" authorId="5" shapeId="0" xr:uid="{ABD68C27-D4A9-44EE-AF6F-3CB8BDA6A138}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</t>
+      </text>
+    </comment>
+    <comment ref="E17" authorId="6" shapeId="0" xr:uid="{F871D504-E335-4464-BC26-F968C341E623}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="7" shapeId="0" xr:uid="{B7BC671D-705C-4D5C-B912-A3612A768BDC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="8" shapeId="0" xr:uid="{F677BA5A-9EB4-4E49-B10C-8863788FBC2A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="9" shapeId="0" xr:uid="{4A07708A-FC38-41EF-A05C-7D7649D41200}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="I17" authorId="10" shapeId="0" xr:uid="{0AB730C8-C4B5-42EB-BB13-7117616499F2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</t>
+      </text>
+    </comment>
+    <comment ref="J17" authorId="11" shapeId="0" xr:uid="{A6EB124F-E722-4A46-855B-1045507D0D74}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All potential cases of verbal harmonization/disharmonization, forward and backward.</t>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="12" shapeId="0" xr:uid="{12F049EC-7824-407C-8639-62FB5D5BDF75}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that harmonized to parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="13" shapeId="0" xr:uid="{6765579E-3E10-490D-89EC-59DA74345D48}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that disharmonized from  parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="14" shapeId="0" xr:uid="{52E5C178-4B24-4FDF-9343-87C45F414C4B}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3534,7 +3615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1" shapeId="0" xr:uid="{EDB8B4AC-3BBA-4CF2-9124-E7EB8C1DED14}">
+    <comment ref="L3" authorId="1" shapeId="0" xr:uid="{EDB8B4AC-3BBA-4CF2-9124-E7EB8C1DED14}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3542,7 +3623,7 @@
     The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</t>
       </text>
     </comment>
-    <comment ref="K4" authorId="2" shapeId="0" xr:uid="{4A6E7644-07DF-4FD6-9302-D422929EAE16}">
+    <comment ref="L4" authorId="2" shapeId="0" xr:uid="{4A6E7644-07DF-4FD6-9302-D422929EAE16}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3550,7 +3631,7 @@
     That is, the autograph contains a singular reading and the apograph followed it</t>
       </text>
     </comment>
-    <comment ref="K5" authorId="3" shapeId="0" xr:uid="{32705B44-288D-406D-BD26-12545BB4005C}">
+    <comment ref="L5" authorId="3" shapeId="0" xr:uid="{32705B44-288D-406D-BD26-12545BB4005C}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -3558,7 +3639,7 @@
     The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</t>
       </text>
     </comment>
-    <comment ref="M13" authorId="4" shapeId="0" xr:uid="{50EF6C78-A584-4EFD-962E-4F6FBECA67ED}">
+    <comment ref="N13" authorId="4" shapeId="0" xr:uid="{50EF6C78-A584-4EFD-962E-4F6FBECA67ED}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -7207,6 +7288,15 @@
     <author>tc={F68261FB-0759-419B-99E1-7FA6E8A96D8A}</author>
     <author>tc={D3AB1C5E-37EE-4B0D-8A88-F4E34FC5C971}</author>
     <author>tc={23119399-1739-43B4-B611-B745C310A73E}</author>
+    <author>tc={3530E2A4-BA91-4BEE-B467-85249F7B65F2}</author>
+    <author>tc={7A2E0601-0730-4EE0-8DC1-2C604FE734E2}</author>
+    <author>tc={AB40FD5F-DECE-4979-ABB4-A4A8BEABFB37}</author>
+    <author>tc={4DF0DCA2-4D8C-49E2-90B6-CC9B0F9E5168}</author>
+    <author>tc={2BF192EC-6060-484A-9533-CF1D32256CB0}</author>
+    <author>tc={2A118E27-7F34-40C0-B28E-CBEB4C8A2422}</author>
+    <author>tc={EDF6A1E8-7553-4F3A-8871-E63AF921FC29}</author>
+    <author>tc={473585F0-164E-4E71-ABDE-8E88A8B1A2A0}</author>
+    <author>tc={AFCC7E41-5650-40F5-A984-14DD32C7686D}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{8D88016F-DF6D-4157-B428-26D5A2649EB4}">
@@ -7612,7 +7702,7 @@
     For substitutions, the word frequency of the autograph reading</t>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{B552E300-4707-47D1-BFBD-AB0FF15F2C87}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{B552E300-4707-47D1-BFBD-AB0FF15F2C87}">
       <text>
         <r>
           <rPr>
@@ -7636,7 +7726,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{9DD44A70-E978-454A-8B43-50059993E5A0}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{9DD44A70-E978-454A-8B43-50059993E5A0}">
       <text>
         <r>
           <rPr>
@@ -7660,7 +7750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{C147553B-3907-4389-A21E-F5EB4B113188}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{C147553B-3907-4389-A21E-F5EB4B113188}">
       <text>
         <r>
           <rPr>
@@ -7684,7 +7774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{136849F0-345C-48CD-AD48-649189436E73}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{136849F0-345C-48CD-AD48-649189436E73}">
       <text>
         <r>
           <rPr>
@@ -7708,7 +7798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{5C05C3F3-58E1-485B-B282-50F5C6B3D0BF}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{5C05C3F3-58E1-485B-B282-50F5C6B3D0BF}">
       <text>
         <r>
           <rPr>
@@ -7733,7 +7823,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{633D98EF-BF25-4107-801F-D20308C895C7}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{633D98EF-BF25-4107-801F-D20308C895C7}">
       <text>
         <r>
           <rPr>
@@ -7757,7 +7847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{56B4F415-8E62-46BA-9F59-271434352C92}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{56B4F415-8E62-46BA-9F59-271434352C92}">
       <text>
         <r>
           <rPr>
@@ -7781,7 +7871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="3" shapeId="0" xr:uid="{F68261FB-0759-419B-99E1-7FA6E8A96D8A}">
+    <comment ref="D21" authorId="3" shapeId="0" xr:uid="{F68261FB-0759-419B-99E1-7FA6E8A96D8A}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -7789,7 +7879,7 @@
     The number of variants that harmonized to parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D24" authorId="4" shapeId="0" xr:uid="{D3AB1C5E-37EE-4B0D-8A88-F4E34FC5C971}">
+    <comment ref="D22" authorId="4" shapeId="0" xr:uid="{D3AB1C5E-37EE-4B0D-8A88-F4E34FC5C971}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -7797,7 +7887,79 @@
     The number of variants that disharmonized from  parallel phrases in the near context</t>
       </text>
     </comment>
-    <comment ref="D25" authorId="5" shapeId="0" xr:uid="{23119399-1739-43B4-B611-B745C310A73E}">
+    <comment ref="D23" authorId="5" shapeId="0" xr:uid="{23119399-1739-43B4-B611-B745C310A73E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</t>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="6" shapeId="0" xr:uid="{3530E2A4-BA91-4BEE-B467-85249F7B65F2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="F27" authorId="7" shapeId="0" xr:uid="{7A2E0601-0730-4EE0-8DC1-2C604FE734E2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="8" shapeId="0" xr:uid="{AB40FD5F-DECE-4979-ABB4-A4A8BEABFB37}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="9" shapeId="0" xr:uid="{4DF0DCA2-4D8C-49E2-90B6-CC9B0F9E5168}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All cases where influence from following material was possible.</t>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="10" shapeId="0" xr:uid="{2BF192EC-6060-484A-9533-CF1D32256CB0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</t>
+      </text>
+    </comment>
+    <comment ref="J27" authorId="11" shapeId="0" xr:uid="{2A118E27-7F34-40C0-B28E-CBEB4C8A2422}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    All potential cases of verbal harmonization/disharmonization, forward and backward.</t>
+      </text>
+    </comment>
+    <comment ref="D28" authorId="12" shapeId="0" xr:uid="{EDF6A1E8-7553-4F3A-8871-E63AF921FC29}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that harmonized to parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D29" authorId="13" shapeId="0" xr:uid="{473585F0-164E-4E71-ABDE-8E88A8B1A2A0}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The number of variants that disharmonized from  parallel phrases in the near context</t>
+      </text>
+    </comment>
+    <comment ref="D30" authorId="14" shapeId="0" xr:uid="{AFCC7E41-5650-40F5-A984-14DD32C7686D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -9356,7 +9518,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5708" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5712" uniqueCount="912">
   <si>
     <t>Verse Ref</t>
   </si>
@@ -12887,12 +13049,6 @@
     <t>initially skipped 4 lines, skipping to 14:4, before correcting (13v.2.11-14; visual cues present)</t>
   </si>
   <si>
-    <t>twice in this verse the autograph follows the structure τον μοσχον/χιμαρον τον περι της αμαρτιας; the apograph deviates both times</t>
-  </si>
-  <si>
-    <t>twice in this verse the autograph follows the structure τον μοσχον/χιμαρον τον περι της αμαρτιας; the apograph deviates both times; for now, I will call these both disharmonizations, since they depart from a pattern in the autograph</t>
-  </si>
-  <si>
     <t>initially skipped a line (22v.2.7-8; possible visual cues present), then partially corrected but still left the numeral β omitted; frequency = αμωμοσ - δυο</t>
   </si>
   <si>
@@ -12900,6 +13056,36 @@
   </si>
   <si>
     <t>autograph matches usage from 4:14 on prior page (αμαρτια ην ημαρτον)</t>
+  </si>
+  <si>
+    <t>Harmonization_Direction</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Backward</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>Directionality</t>
+  </si>
+  <si>
+    <t>Forward (Exclusive)</t>
+  </si>
+  <si>
+    <t>Forward (Inclusive)</t>
+  </si>
+  <si>
+    <t>Backward (Exclusive)</t>
+  </si>
+  <si>
+    <t>Backward (Inclusive)</t>
+  </si>
+  <si>
+    <t>twice in this verse the autograph follows the structure τον μοσχον/χιμαρον τον περι της αμαρτιας; that the apograph deviates both times would leave disharmonization undetectable</t>
   </si>
 </sst>
 </file>
@@ -13033,7 +13219,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="366">
+  <dxfs count="364">
     <dxf>
       <fill>
         <patternFill>
@@ -13071,17 +13257,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -13568,28 +13743,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
@@ -13614,6 +13767,28 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -13788,13 +13963,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -13813,6 +13981,13 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -14232,7 +14407,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
       <border>
@@ -14243,7 +14418,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -14287,17 +14462,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
@@ -14330,6 +14494,17 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
@@ -14341,8 +14516,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -14451,6 +14626,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -14458,13 +14640,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -14761,17 +14936,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -16387,17 +16551,6 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
         </patternFill>
@@ -16444,6 +16597,17 @@
       <fill>
         <patternFill patternType="none">
           <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
       <border>
@@ -16618,6 +16782,17 @@
     </dxf>
     <dxf>
       <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
@@ -16631,17 +16806,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border>
@@ -16735,6 +16899,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
@@ -16745,8 +16916,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -16754,13 +16925,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
         </patternFill>
       </fill>
     </dxf>
@@ -17241,13 +17405,40 @@
   <threadedComment ref="T1" dT="2024-01-16T09:59:48.08" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{7D0F0819-F314-44D2-8676-B26B3DADBD37}">
     <text>For substitutions, the word frequency of the autograph reading</text>
   </threadedComment>
-  <threadedComment ref="D13" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{2E137862-4F64-4708-9E15-347B1D3C02B6}">
+  <threadedComment ref="D11" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{2E137862-4F64-4708-9E15-347B1D3C02B6}">
     <text>The number of variants that harmonized to parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D14" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{8815700D-36AA-4FB8-AF8E-41A4B7606096}">
+  <threadedComment ref="D12" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{8815700D-36AA-4FB8-AF8E-41A4B7606096}">
     <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D15" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{ABD68C27-D4A9-44EE-AF6F-3CB8BDA6A138}">
+  <threadedComment ref="D13" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{ABD68C27-D4A9-44EE-AF6F-3CB8BDA6A138}">
+    <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
+  </threadedComment>
+  <threadedComment ref="E17" dT="2026-03-27T21:09:00.40" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{F871D504-E335-4464-BC26-F968C341E623}">
+    <text>ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="F17" dT="2026-03-26T18:54:36.97" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{B7BC671D-705C-4D5C-B912-A3612A768BDC}">
+    <text>All cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="G17" dT="2026-03-27T21:09:12.56" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{F677BA5A-9EB4-4E49-B10C-8863788FBC2A}">
+    <text>ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="H17" dT="2026-03-26T18:55:05.59" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{4A07708A-FC38-41EF-A05C-7D7649D41200}">
+    <text>All cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="I17" dT="2026-03-26T18:56:11.72" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{0AB730C8-C4B5-42EB-BB13-7117616499F2}">
+    <text>Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</text>
+  </threadedComment>
+  <threadedComment ref="J17" dT="2026-03-26T18:56:36.44" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{A6EB124F-E722-4A46-855B-1045507D0D74}">
+    <text>All potential cases of verbal harmonization/disharmonization, forward and backward.</text>
+  </threadedComment>
+  <threadedComment ref="D18" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{12F049EC-7824-407C-8639-62FB5D5BDF75}">
+    <text>The number of variants that harmonized to parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D19" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{6765579E-3E10-490D-89EC-59DA74345D48}">
+    <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D20" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{52E5C178-4B24-4FDF-9343-87C45F414C4B}">
     <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
   </threadedComment>
 </ThreadedComments>
@@ -17275,16 +17466,16 @@
 
 <file path=xl/threadedComments/threadedComment15.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="K3" dT="2023-08-03T13:34:30.53" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{EDB8B4AC-3BBA-4CF2-9124-E7EB8C1DED14}">
+  <threadedComment ref="L3" dT="2023-08-03T13:34:30.53" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{EDB8B4AC-3BBA-4CF2-9124-E7EB8C1DED14}">
     <text>The apograph reading is singular and the autograph reading is not. The singular readings method would detect this variant</text>
   </threadedComment>
-  <threadedComment ref="K4" dT="2023-08-03T13:33:28.57" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{4A6E7644-07DF-4FD6-9302-D422929EAE16}">
+  <threadedComment ref="L4" dT="2023-08-03T13:33:28.57" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{4A6E7644-07DF-4FD6-9302-D422929EAE16}">
     <text>That is, the autograph contains a singular reading and the apograph followed it</text>
   </threadedComment>
-  <threadedComment ref="K5" dT="2023-08-03T13:35:10.13" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{32705B44-288D-406D-BD26-12545BB4005C}">
+  <threadedComment ref="L5" dT="2023-08-03T13:35:10.13" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{32705B44-288D-406D-BD26-12545BB4005C}">
     <text>The apograph reading is not singular: other witnesses contain the same reading. These are real variants produced by the apograph scribe, but the singular readings method would not detect them</text>
   </threadedComment>
-  <threadedComment ref="M13" dT="2023-08-14T14:21:11.11" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{50EF6C78-A584-4EFD-962E-4F6FBECA67ED}">
+  <threadedComment ref="N13" dT="2023-08-14T14:21:11.11" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{50EF6C78-A584-4EFD-962E-4F6FBECA67ED}">
     <text>For words which have multiple common forms not impacting their inflection (e.g., ουκ-ουχ-ου, επι-επ-εφ)</text>
   </threadedComment>
 </ThreadedComments>
@@ -17593,13 +17784,40 @@
   <threadedComment ref="T1" dT="2024-01-16T09:59:48.08" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{AC8776E7-AFF7-419D-BA47-24BB3D8C7939}">
     <text>For substitutions, the word frequency of the autograph reading</text>
   </threadedComment>
-  <threadedComment ref="D23" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{F68261FB-0759-419B-99E1-7FA6E8A96D8A}">
+  <threadedComment ref="D21" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{F68261FB-0759-419B-99E1-7FA6E8A96D8A}">
     <text>The number of variants that harmonized to parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D24" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{D3AB1C5E-37EE-4B0D-8A88-F4E34FC5C971}">
+  <threadedComment ref="D22" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{D3AB1C5E-37EE-4B0D-8A88-F4E34FC5C971}">
     <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
   </threadedComment>
-  <threadedComment ref="D25" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{23119399-1739-43B4-B611-B745C310A73E}">
+  <threadedComment ref="D23" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{23119399-1739-43B4-B611-B745C310A73E}">
+    <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
+  </threadedComment>
+  <threadedComment ref="E27" dT="2026-03-27T21:09:00.40" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{3530E2A4-BA91-4BEE-B467-85249F7B65F2}">
+    <text>ONLY those cases where influence from preceding material was possible and EXCLUDING cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="F27" dT="2026-03-26T18:54:36.97" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{7A2E0601-0730-4EE0-8DC1-2C604FE734E2}">
+    <text>All cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="G27" dT="2026-03-27T21:09:12.56" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{AB40FD5F-DECE-4979-ABB4-A4A8BEABFB37}">
+    <text>ONLY those cases where influence from following material was possible and EXCLUDING cases where influence from preceding material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="H27" dT="2026-03-26T18:55:05.59" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{4DF0DCA2-4D8C-49E2-90B6-CC9B0F9E5168}">
+    <text>All cases where influence from following material was possible.</text>
+  </threadedComment>
+  <threadedComment ref="I27" dT="2026-03-26T18:56:11.72" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{2BF192EC-6060-484A-9533-CF1D32256CB0}">
+    <text>Only cases where verbal parallels existed both behind and after the variant in question and the direction of change in verbal similarity was the same.</text>
+  </threadedComment>
+  <threadedComment ref="J27" dT="2026-03-26T18:56:36.44" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{2A118E27-7F34-40C0-B28E-CBEB4C8A2422}">
+    <text>All potential cases of verbal harmonization/disharmonization, forward and backward.</text>
+  </threadedComment>
+  <threadedComment ref="D28" dT="2024-01-24T17:15:11.25" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{EDF6A1E8-7553-4F3A-8871-E63AF921FC29}">
+    <text>The number of variants that harmonized to parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D29" dT="2024-01-24T17:15:35.01" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{473585F0-164E-4E71-ABDE-8E88A8B1A2A0}">
+    <text>The number of variants that disharmonized from  parallel phrases in the near context</text>
+  </threadedComment>
+  <threadedComment ref="D30" dT="2024-01-24T17:16:15.06" personId="{726B0DE7-C665-4EBE-970E-5803EF78B313}" id="{AFCC7E41-5650-40F5-A984-14DD32C7686D}">
     <text>The ratio of harmonizations to disharmonizations; = harmonizations / (harmonizations + disharmonizations)</text>
   </threadedComment>
 </ThreadedComments>
@@ -17755,7 +17973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A644991-2036-4936-8ECE-AA604E1C2B0C}">
-  <dimension ref="A1:AH253"/>
+  <dimension ref="A1:AH254"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
@@ -21343,7 +21561,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="84" spans="1:33" ht="29">
+    <row r="84" spans="1:33" ht="43.5">
       <c r="A84" s="1" t="s">
         <v>121</v>
       </c>
@@ -24279,7 +24497,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="158" spans="1:33" ht="130.5">
+    <row r="158" spans="1:33" ht="145">
       <c r="A158" s="1" t="s">
         <v>438</v>
       </c>
@@ -24479,11 +24697,13 @@
       <c r="E163" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F163" s="1"/>
+      <c r="F163" s="1" t="s">
+        <v>523</v>
+      </c>
       <c r="G163" s="1"/>
       <c r="H163" s="1"/>
       <c r="I163" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="J163" s="7" t="s">
         <v>504</v>
@@ -24535,11 +24755,13 @@
       <c r="E164" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="F164" s="1"/>
+      <c r="F164" s="1" t="s">
+        <v>523</v>
+      </c>
       <c r="G164" s="1"/>
       <c r="H164" s="1"/>
       <c r="I164" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="J164" s="7" t="s">
         <v>504</v>
@@ -27654,7 +27876,7 @@
         <v>499</v>
       </c>
       <c r="I242" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="J242" s="7" t="s">
         <v>548</v>
@@ -27924,177 +28146,184 @@
     <row r="253" spans="1:33">
       <c r="Q253" s="8"/>
     </row>
+    <row r="254" spans="1:33">
+      <c r="E254">
+        <f>COUNTIF(F:F, "Autograph transcript error, but still a variant") + COUNTIF(F:F, "Apograph transcript error, but still a variant") + COUNTIF(F:F, "Not a variant: autograph transcript error") + COUNTIF(F:F, "Not a variant: apograph transcript error")</f>
+        <v>10</v>
+      </c>
+      <c r="Q254" s="8"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J1048576">
-    <cfRule type="expression" dxfId="365" priority="29">
+    <cfRule type="expression" dxfId="363" priority="30">
+      <formula>$J2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="362" priority="29">
       <formula>$J2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="364" priority="30">
-      <formula>$J2=""</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:O254 R2:S254">
+    <cfRule type="expression" dxfId="361" priority="28">
+      <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:O253 R2:S253">
-    <cfRule type="expression" dxfId="363" priority="27">
+    <cfRule type="expression" dxfId="360" priority="27">
       <formula>AND(OR($J2="Addition",$J2="Omission"), K2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="362" priority="28">
-      <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:S1048576">
-    <cfRule type="expression" dxfId="361" priority="26">
+    <cfRule type="expression" dxfId="359" priority="26">
       <formula>AND(OR($J2="Addition",$J2="Omission"), K2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N1048576">
-    <cfRule type="expression" dxfId="360" priority="21">
+    <cfRule type="expression" dxfId="358" priority="21">
       <formula>AND($L2&lt;&gt;"",$L2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:Q253">
-    <cfRule type="expression" dxfId="359" priority="19">
+  <conditionalFormatting sqref="P2:Q254">
+    <cfRule type="expression" dxfId="357" priority="19">
       <formula>AND(OR($J2="Addition",$J2="Omission"), P2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="358" priority="20">
+    <cfRule type="expression" dxfId="356" priority="20">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:Q1048576">
-    <cfRule type="expression" dxfId="357" priority="17">
+    <cfRule type="expression" dxfId="355" priority="17">
       <formula>$O2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="356" priority="18">
+    <cfRule type="expression" dxfId="354" priority="18">
       <formula>$O2="NA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R88 R91:R253">
-    <cfRule type="expression" dxfId="355" priority="22">
+  <conditionalFormatting sqref="R2:R88 R91:R254">
+    <cfRule type="expression" dxfId="353" priority="22">
       <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R89">
-    <cfRule type="expression" dxfId="354" priority="78">
+    <cfRule type="expression" dxfId="352" priority="78">
       <formula>AND(OR($J89="Addition",$J89="Omission",$J89="Substitution - Word"),RIGHT($AE89,6)&lt;&gt;"strict",$AD90&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R90">
-    <cfRule type="expression" dxfId="353" priority="79">
+    <cfRule type="expression" dxfId="351" priority="79">
       <formula>AND(OR($J90="Addition",$J90="Omission",$J90="Substitution - Word"),RIGHT($AE90,6)&lt;&gt;"strict",#REF!&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:V1048576">
-    <cfRule type="expression" dxfId="352" priority="23">
+    <cfRule type="expression" dxfId="350" priority="24">
+      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="349" priority="25">
+      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="348" priority="23">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="351" priority="24">
-      <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="350" priority="25">
-      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W88 W91:W253">
-    <cfRule type="expression" dxfId="349" priority="13">
+  <conditionalFormatting sqref="W2:W88 W91:W254">
+    <cfRule type="expression" dxfId="347" priority="13">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W88 W91:W1048576">
-    <cfRule type="expression" dxfId="348" priority="7">
+    <cfRule type="expression" dxfId="346" priority="7">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="347" priority="8">
+    <cfRule type="expression" dxfId="345" priority="8">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W27">
-    <cfRule type="expression" dxfId="346" priority="9">
+    <cfRule type="expression" dxfId="344" priority="9">
       <formula>AND($J27&lt;&gt;"",$J27&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="345" priority="12">
+    <cfRule type="expression" dxfId="343" priority="12">
       <formula>OR($J27="",$J27="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W89">
-    <cfRule type="expression" dxfId="344" priority="88">
+    <cfRule type="expression" dxfId="342" priority="88">
       <formula>AND($AD90&lt;&gt;"Yes",$AE89="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="343" priority="94">
+    <cfRule type="expression" dxfId="341" priority="94">
       <formula>AND($W89&lt;&gt;"",OR($AD90="Yes",$AE89&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="342" priority="95">
+    <cfRule type="expression" dxfId="340" priority="95">
       <formula>OR($AD90="Yes",$AE89&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W90">
-    <cfRule type="expression" dxfId="341" priority="91">
+    <cfRule type="expression" dxfId="339" priority="91">
       <formula>AND(#REF!&lt;&gt;"Yes",$AE90="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="340" priority="96">
+    <cfRule type="expression" dxfId="338" priority="96">
       <formula>AND($W90&lt;&gt;"",OR(#REF!="Yes",$AE90&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="339" priority="97">
+    <cfRule type="expression" dxfId="337" priority="97">
       <formula>OR(#REF!="Yes",$AE90&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W89:AB90 AE89:AF90 W2:AF26 W28:AF88 W91:AF253">
-    <cfRule type="expression" dxfId="338" priority="70">
+  <conditionalFormatting sqref="W89:AB90 AE89:AF90 W2:AF26 W28:AF88 W91:AF254">
+    <cfRule type="expression" dxfId="336" priority="70">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:AF26 W28:AF88 W91:AF253">
-    <cfRule type="expression" dxfId="337" priority="36">
+  <conditionalFormatting sqref="W89:AB90 AE89:AF90">
+    <cfRule type="expression" dxfId="335" priority="69">
+      <formula>AND($J89&lt;&gt;"",$J89&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W2:AF26 W28:AF88 W91:AF254">
+    <cfRule type="expression" dxfId="334" priority="36">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W89:AB90 AE89:AF90">
-    <cfRule type="expression" dxfId="336" priority="69">
-      <formula>AND($J89&lt;&gt;"",$J89&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="X2:X1048576">
-    <cfRule type="expression" dxfId="335" priority="4">
+    <cfRule type="expression" dxfId="333" priority="4">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X27">
-    <cfRule type="expression" dxfId="334" priority="5">
+    <cfRule type="expression" dxfId="332" priority="6">
+      <formula>OR($J27="",$J27="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="331" priority="5">
       <formula>AND($J27&lt;&gt;"",$J27&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="333" priority="6">
-      <formula>OR($J27="",$J27="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y1048576">
-    <cfRule type="expression" dxfId="332" priority="10">
+    <cfRule type="expression" dxfId="330" priority="11">
+      <formula>$X2=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="329" priority="10">
       <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="331" priority="11">
-      <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y27:AF27">
-    <cfRule type="expression" dxfId="330" priority="15">
+    <cfRule type="expression" dxfId="328" priority="16">
+      <formula>OR($J27="",$J27="Unclear due to correction")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="327" priority="15">
       <formula>AND($J27&lt;&gt;"",$J27&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="329" priority="16">
-      <formula>OR($J27="",$J27="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC90:AD90">
-    <cfRule type="expression" dxfId="328" priority="100">
+    <cfRule type="expression" dxfId="326" priority="100">
       <formula>AND($J89&lt;&gt;"",$J89&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="327" priority="101">
+    <cfRule type="expression" dxfId="325" priority="101">
       <formula>OR($J89="",$J89="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD88 AD91:AD1048576">
-    <cfRule type="expression" dxfId="326" priority="14">
+    <cfRule type="expression" dxfId="324" priority="14">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD90">
-    <cfRule type="expression" dxfId="325" priority="106">
+    <cfRule type="expression" dxfId="323" priority="106">
       <formula>AND(OR($AB89&lt;&gt;"",$AC90&lt;&gt;""),$AD90="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -28126,6 +28355,12 @@
             <xm:f>'Data Regularization'!$C$2:$C$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H26 H28:H1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77995993-73E5-491D-A019-F00DED2E1F23}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$D$3:$D$1048576</xm:f>
+          </x14:formula1>
+          <xm:sqref>I247:I1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2975F693-B08D-4742-96D9-BE6AA2A12246}">
           <x14:formula1>
@@ -28159,57 +28394,51 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{DAADCD28-16E1-48E4-BA3E-63AB0A27F900}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X26 X28:X1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{04EBE815-A8A3-4207-9E11-F54E9DDD3BBC}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z26 Z28:Z1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EF181607-0144-40B2-A542-38C97D702924}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y26 Y28:Y1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{528722DE-E174-4D17-AE39-B32BB55DC156}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA26 AA28:AA1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C4205F39-68DA-4853-B3BF-18F694B51B85}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB26 AB28:AB1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0CCDFBC2-E088-4711-9BB3-8DAF03F70EEF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE26 AE28:AE1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E746F375-F709-42B7-BAA9-ADDB0DB846A3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF26 AF28:AF1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2108E825-402E-4594-9CCC-0B41519E6EED}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD26 AD28:AD88 AD90:AD1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{77995993-73E5-491D-A019-F00DED2E1F23}">
-          <x14:formula1>
-            <xm:f>'Data Regularization'!$D$3:$D$1048576</xm:f>
-          </x14:formula1>
-          <xm:sqref>I247:I1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -29457,113 +29686,113 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G17">
-    <cfRule type="expression" dxfId="108" priority="24">
+    <cfRule type="expression" dxfId="107" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="25">
+    <cfRule type="expression" dxfId="106" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L17 O2:P17">
-    <cfRule type="expression" dxfId="106" priority="22">
+    <cfRule type="expression" dxfId="105" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="23">
+    <cfRule type="expression" dxfId="104" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P17">
-    <cfRule type="expression" dxfId="104" priority="21">
+    <cfRule type="expression" dxfId="103" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K17">
-    <cfRule type="expression" dxfId="103" priority="16">
+    <cfRule type="expression" dxfId="102" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N17">
-    <cfRule type="expression" dxfId="102" priority="12">
+    <cfRule type="expression" dxfId="101" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="13">
+    <cfRule type="expression" dxfId="100" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="14">
+    <cfRule type="expression" dxfId="99" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="15">
+    <cfRule type="expression" dxfId="98" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O17">
-    <cfRule type="expression" dxfId="98" priority="17">
+    <cfRule type="expression" dxfId="97" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q25">
-    <cfRule type="expression" dxfId="97" priority="2">
+    <cfRule type="expression" dxfId="96" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="3">
+    <cfRule type="expression" dxfId="95" priority="3">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="4">
+    <cfRule type="expression" dxfId="94" priority="4">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T17">
-    <cfRule type="expression" dxfId="94" priority="18">
+    <cfRule type="expression" dxfId="93" priority="18">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="19">
+    <cfRule type="expression" dxfId="92" priority="19">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="20">
+    <cfRule type="expression" dxfId="91" priority="20">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U17">
-    <cfRule type="expression" dxfId="91" priority="6">
+    <cfRule type="expression" dxfId="90" priority="6">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="90" priority="7">
+    <cfRule type="expression" dxfId="89" priority="7">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="10">
+    <cfRule type="expression" dxfId="88" priority="10">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD6">
-    <cfRule type="expression" dxfId="88" priority="26">
+    <cfRule type="expression" dxfId="87" priority="26">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD17">
-    <cfRule type="expression" dxfId="87" priority="27">
+    <cfRule type="expression" dxfId="86" priority="27">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U7:AD17">
-    <cfRule type="expression" dxfId="86" priority="1">
+    <cfRule type="expression" dxfId="85" priority="1">
       <formula>AND($I7&lt;&gt;"",$I7&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V17">
-    <cfRule type="expression" dxfId="85" priority="5">
+    <cfRule type="expression" dxfId="84" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W17">
-    <cfRule type="expression" dxfId="84" priority="8">
+    <cfRule type="expression" dxfId="83" priority="8">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="9">
+    <cfRule type="expression" dxfId="82" priority="9">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB17">
-    <cfRule type="expression" dxfId="82" priority="11">
+    <cfRule type="expression" dxfId="81" priority="11">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29628,49 +29857,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{0A835A24-AE45-49FD-96F1-18B3403D29CF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D8938D31-CADD-4384-9A76-780B28AE87B8}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B947EEC-1614-46A7-8518-0758308D95D4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{86F1BF84-6701-45DA-BC1A-74B742E0DD96}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{725E1C55-94A4-4DF7-AB9E-CDCD34D80D03}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7539E16D-FF37-45E4-964C-821F5F92AE7B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CC49AD09-06BD-44D6-8AF7-F27081382B13}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2E9549F9-1C3C-4D8C-9E29-EEB96D8D374E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB17</xm:sqref>
         </x14:dataValidation>
@@ -29933,134 +30162,134 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2">
-    <cfRule type="expression" dxfId="81" priority="35">
+    <cfRule type="expression" dxfId="80" priority="35">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="36">
+    <cfRule type="expression" dxfId="79" priority="36">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L2">
-    <cfRule type="expression" dxfId="79" priority="33">
+    <cfRule type="expression" dxfId="78" priority="33">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="34">
+    <cfRule type="expression" dxfId="77" priority="34">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P2">
-    <cfRule type="expression" dxfId="77" priority="32">
+    <cfRule type="expression" dxfId="76" priority="32">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2">
-    <cfRule type="expression" dxfId="76" priority="28">
+    <cfRule type="expression" dxfId="75" priority="28">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N2">
-    <cfRule type="expression" dxfId="75" priority="24">
+    <cfRule type="expression" dxfId="74" priority="26">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="25">
+      <formula>$N2="NA"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="24">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="25">
-      <formula>$N2="NA"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="73" priority="26">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="27">
+    <cfRule type="expression" dxfId="71" priority="27">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2">
-    <cfRule type="expression" dxfId="71" priority="16">
+    <cfRule type="expression" dxfId="70" priority="16">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:P2">
-    <cfRule type="expression" dxfId="70" priority="19">
+    <cfRule type="expression" dxfId="69" priority="19">
       <formula>AND(OR($I2="Addition",$I2="Omission"), O2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="20">
+    <cfRule type="expression" dxfId="68" priority="20">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="expression" dxfId="68" priority="1">
+    <cfRule type="expression" dxfId="67" priority="1">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="2">
+    <cfRule type="expression" dxfId="66" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="3">
+    <cfRule type="expression" dxfId="65" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2">
-    <cfRule type="expression" dxfId="65" priority="29">
+    <cfRule type="expression" dxfId="64" priority="29">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$V2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="30">
+    <cfRule type="expression" dxfId="63" priority="30">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$V2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="31">
+    <cfRule type="expression" dxfId="62" priority="31">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:T2">
-    <cfRule type="expression" dxfId="62" priority="7">
+    <cfRule type="expression" dxfId="61" priority="7">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="8">
+    <cfRule type="expression" dxfId="60" priority="8">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="9">
+    <cfRule type="expression" dxfId="59" priority="9">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="10">
+    <cfRule type="expression" dxfId="58" priority="10">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="11">
+    <cfRule type="expression" dxfId="57" priority="11">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="12">
+    <cfRule type="expression" dxfId="56" priority="12">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="expression" dxfId="56" priority="13">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="55" priority="14">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" dxfId="54" priority="37">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="53" priority="13">
+      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD2">
-    <cfRule type="expression" dxfId="53" priority="17">
-      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="52" priority="18">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="51" priority="17">
+      <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2">
-    <cfRule type="expression" dxfId="51" priority="21">
+    <cfRule type="expression" dxfId="50" priority="21">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2">
-    <cfRule type="expression" dxfId="50" priority="22">
+    <cfRule type="expression" dxfId="49" priority="22">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="23">
+    <cfRule type="expression" dxfId="48" priority="23">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2">
-    <cfRule type="expression" dxfId="48" priority="15">
+    <cfRule type="expression" dxfId="47" priority="15">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30124,49 +30353,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{0BF0680E-4DEA-410B-8538-2D25C7341C27}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{652D5401-42DF-46A5-AE0C-3CA5A5CEA2FD}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B802C206-6845-4ACB-9904-8300A4164327}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF2E1D58-2796-4854-94EE-06B7FCC9E509}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47FDAE82-4C7D-4A59-B9FF-2BFD401F92A2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{21A45BB2-FEE6-4816-B317-A011B2391DE8}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7149DE23-3D98-4962-B6BF-1238BCFE05A5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CABD0CB7-8FFC-4E8B-B271-3957CB8BF4C9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2</xm:sqref>
         </x14:dataValidation>
@@ -30855,102 +31084,102 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="expression" dxfId="47" priority="24">
+    <cfRule type="expression" dxfId="46" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="25">
+    <cfRule type="expression" dxfId="45" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L9 O2:P9">
-    <cfRule type="expression" dxfId="45" priority="22">
+    <cfRule type="expression" dxfId="44" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="23">
+    <cfRule type="expression" dxfId="43" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P9">
-    <cfRule type="expression" dxfId="43" priority="21">
+    <cfRule type="expression" dxfId="42" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K9">
-    <cfRule type="expression" dxfId="42" priority="16">
+    <cfRule type="expression" dxfId="41" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N9">
-    <cfRule type="expression" dxfId="41" priority="12">
+    <cfRule type="expression" dxfId="40" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="13">
+    <cfRule type="expression" dxfId="39" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="14">
+    <cfRule type="expression" dxfId="38" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="15">
+    <cfRule type="expression" dxfId="37" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O9">
-    <cfRule type="expression" dxfId="37" priority="17">
+    <cfRule type="expression" dxfId="36" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AG2,6)&lt;&gt;"strict",$AF2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:V9">
-    <cfRule type="expression" dxfId="36" priority="2">
+    <cfRule type="expression" dxfId="35" priority="2">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="3">
+    <cfRule type="expression" dxfId="34" priority="3">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="4">
+    <cfRule type="expression" dxfId="33" priority="4">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W9">
-    <cfRule type="expression" dxfId="33" priority="6">
+    <cfRule type="expression" dxfId="32" priority="6">
       <formula>AND($Y2&lt;&gt;"",OR($AF2="Yes",$AG2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="7">
+    <cfRule type="expression" dxfId="31" priority="7">
       <formula>OR($AF2="Yes",$AG2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="10">
+    <cfRule type="expression" dxfId="30" priority="10">
       <formula>AND($AF2&lt;&gt;"Yes",$AG2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AF3">
-    <cfRule type="expression" dxfId="30" priority="26">
+    <cfRule type="expression" dxfId="29" priority="26">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AF9">
-    <cfRule type="expression" dxfId="29" priority="27">
+    <cfRule type="expression" dxfId="28" priority="27">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W4:AF9">
-    <cfRule type="expression" dxfId="28" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>AND($I4&lt;&gt;"",$I4&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X9">
-    <cfRule type="expression" dxfId="27" priority="5">
+    <cfRule type="expression" dxfId="26" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$Z2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y9">
-    <cfRule type="expression" dxfId="26" priority="8">
+    <cfRule type="expression" dxfId="25" priority="8">
       <formula>AND($Z2="Yes",$AA2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="9">
+    <cfRule type="expression" dxfId="24" priority="9">
       <formula>$Z2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD9">
-    <cfRule type="expression" dxfId="24" priority="11">
+    <cfRule type="expression" dxfId="23" priority="11">
       <formula>AND(OR($AD2&lt;&gt;"",$AE2&lt;&gt;""),$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31015,49 +31244,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{57A91794-7D6A-4666-8250-7EF7C739ECB9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{12559109-4626-4E1F-B2D5-4F966BD1C001}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{965897F5-48CD-4F34-AD47-F1B48FDD6724}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6C7E2A95-0B12-486F-9E02-8D6366E6BDE5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E343B0A-216A-4EB0-8EFD-4AAD90350993}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EB96221A-C89B-4C43-AE8B-8CFCE2EF546B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0A50E4D-5683-4AD9-ABB7-F311692AE904}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F3D78A7A-1E40-4904-845D-C774BD76479C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD9</xm:sqref>
         </x14:dataValidation>
@@ -31069,10 +31298,10 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823AA605-53FA-415E-B635-629114A0E744}">
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:31" s="2" customFormat="1">
+    <row r="1" spans="1:32" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -31137,37 +31366,40 @@
         <v>527</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="58">
+    <row r="2" spans="1:32" ht="58">
       <c r="A2" s="1" t="s">
         <v>56</v>
       </c>
@@ -31207,22 +31439,25 @@
       <c r="U2" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="V2" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
-      <c r="Y2" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" t="s">
+      <c r="AE2" s="7"/>
+      <c r="AF2" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="43.5">
+    <row r="3" spans="1:32" ht="43.5">
       <c r="A3" s="1" t="s">
         <v>84</v>
       </c>
@@ -31274,22 +31509,25 @@
       <c r="U3" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V3" s="7"/>
+      <c r="V3" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
-      <c r="Y3" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
-      <c r="AE3" t="s">
+      <c r="AE3" s="7"/>
+      <c r="AF3" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="43.5">
+    <row r="4" spans="1:32" ht="43.5">
       <c r="A4" s="1" t="s">
         <v>150</v>
       </c>
@@ -31327,22 +31565,25 @@
       <c r="U4" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V4" s="7"/>
+      <c r="V4" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
-      <c r="Y4" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" t="s">
+      <c r="AE4" s="7"/>
+      <c r="AF4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="29">
+    <row r="5" spans="1:32" ht="29">
       <c r="A5" s="1" t="s">
         <v>195</v>
       </c>
@@ -31382,22 +31623,25 @@
       <c r="U5" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V5" s="7"/>
+      <c r="V5" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Y5" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
-      <c r="AE5" t="s">
+      <c r="AE5" s="7"/>
+      <c r="AF5" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="101.5">
+    <row r="6" spans="1:32" ht="101.5">
       <c r="A6" s="1" t="s">
         <v>215</v>
       </c>
@@ -31449,22 +31693,25 @@
       <c r="U6" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V6" s="7"/>
+      <c r="V6" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-      <c r="Y6" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
-      <c r="AE6" t="s">
+      <c r="AE6" s="7"/>
+      <c r="AF6" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="43.5">
+    <row r="7" spans="1:32" ht="43.5">
       <c r="A7" s="1" t="s">
         <v>219</v>
       </c>
@@ -31504,60 +31751,65 @@
       <c r="U7" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V7" s="7"/>
+      <c r="V7" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
-      <c r="Y7" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
       <c r="AD7" s="7"/>
-      <c r="AE7" t="s">
+      <c r="AE7" s="7"/>
+      <c r="AF7" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="72.5">
+    <row r="8" spans="1:32" ht="87">
       <c r="A8" s="1" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>443</v>
+        <v>494</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>444</v>
+        <v>495</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>900</v>
+        <v>782</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>504</v>
       </c>
       <c r="I8" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8" s="7">
-        <v>3</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>541</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L8" s="7"/>
       <c r="M8" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="N8" s="7"/>
-      <c r="O8" s="8"/>
+        <v>536</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>757</v>
+      </c>
       <c r="P8" s="7"/>
       <c r="Q8" s="7">
-        <v>19277</v>
+        <v>119</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7" t="s">
@@ -31569,283 +31821,267 @@
       <c r="U8" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V8" s="7"/>
+      <c r="V8" s="7" t="s">
+        <v>905</v>
+      </c>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
-      <c r="Y8" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
-      <c r="AE8" t="s">
+      <c r="AE8" s="7"/>
+      <c r="AF8" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="72.5">
-      <c r="A9" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" t="s">
-        <v>900</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="I9" s="7">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7">
-        <v>3</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="N9" s="7"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7">
-        <v>19277</v>
-      </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="7"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AE9" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="87">
-      <c r="A10" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" t="s">
-        <v>782</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="I10" s="7">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7">
-        <v>3</v>
-      </c>
-      <c r="K10" s="7">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7">
-        <v>119</v>
-      </c>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="U10" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="7"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
-      <c r="AE10" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31">
-      <c r="D13" t="s">
+    <row r="11" spans="1:32">
+      <c r="D11" t="s">
         <v>853</v>
       </c>
-      <c r="E13">
+      <c r="E11">
         <f>COUNTIF(U:U, "Harmonizing")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
-      <c r="D14" t="s">
+    <row r="12" spans="1:32">
+      <c r="D12" t="s">
         <v>854</v>
       </c>
-      <c r="E14">
+      <c r="E12">
         <f>COUNTIF(U:U, "Disharmonizing")</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31">
-      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32">
+      <c r="D13" t="s">
         <v>855</v>
       </c>
-      <c r="E15">
-        <f>E13/(E13+E14)</f>
+      <c r="E13">
+        <f>E11/(E11+E12)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:32">
+      <c r="E16" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="4:10">
+      <c r="E17" t="s">
+        <v>907</v>
+      </c>
+      <c r="F17" t="s">
+        <v>908</v>
+      </c>
+      <c r="G17" t="s">
+        <v>909</v>
+      </c>
+      <c r="H17" t="s">
+        <v>910</v>
+      </c>
+      <c r="I17" t="s">
+        <v>905</v>
+      </c>
+      <c r="J17" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="18" spans="4:10">
+      <c r="D18" t="s">
+        <v>853</v>
+      </c>
+      <c r="E18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"forward")</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"forward") + COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"backward")</f>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"backward") + COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f>COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"both") + COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"forward") + COUNTIFS($U$2:$U$8,"Harmonizing",$V$2:$V$8,"backward")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:10">
+      <c r="D19" t="s">
+        <v>854</v>
+      </c>
+      <c r="E19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"forward")</f>
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"forward") + COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"both")</f>
+        <v>3</v>
+      </c>
+      <c r="G19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"backward")</f>
+        <v>4</v>
+      </c>
+      <c r="H19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"backward") + COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"both")</f>
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <f>COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"both") + COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"forward") + COUNTIFS($U$2:$U$8,"Disharmonizing",$V$2:$V$8,"backward")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="4:10">
+      <c r="D20" t="s">
+        <v>855</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20:G20" si="0">E18/(E18+E19)</f>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" ref="H20:J20" si="1">H18/(H18+H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H10">
-    <cfRule type="expression" dxfId="23" priority="21">
+  <mergeCells count="1">
+    <mergeCell ref="E16:J16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H2:H8">
+    <cfRule type="expression" dxfId="22" priority="21">
       <formula>$J2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
+    <cfRule type="expression" dxfId="21" priority="22">
       <formula>$J2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:M10 P2:Q10">
-    <cfRule type="expression" dxfId="21" priority="19">
+  <conditionalFormatting sqref="I2:M8 P2:Q8">
+    <cfRule type="expression" dxfId="20" priority="19">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
+    <cfRule type="expression" dxfId="19" priority="20">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:Q10">
-    <cfRule type="expression" dxfId="19" priority="18">
+  <conditionalFormatting sqref="I2:Q8">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
-    <cfRule type="expression" dxfId="18" priority="13">
+  <conditionalFormatting sqref="L2:L8">
+    <cfRule type="expression" dxfId="17" priority="13">
       <formula>AND($L2&lt;&gt;"",$L2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O10">
-    <cfRule type="expression" dxfId="17" priority="9">
+  <conditionalFormatting sqref="N2:O8">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>$O2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>$O2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="11">
+    <cfRule type="expression" dxfId="14" priority="11">
       <formula>AND(OR($J2="Addition",$J2="Omission"), N2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="12">
+    <cfRule type="expression" dxfId="13" priority="12">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P10">
-    <cfRule type="expression" dxfId="13" priority="14">
-      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
+  <conditionalFormatting sqref="P2:P8">
+    <cfRule type="expression" dxfId="12" priority="14">
+      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AF2,6)&lt;&gt;"strict",$AE2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:T10">
-    <cfRule type="expression" dxfId="12" priority="15">
+  <conditionalFormatting sqref="R2:T8">
+    <cfRule type="expression" dxfId="11" priority="15">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="16">
+    <cfRule type="expression" dxfId="10" priority="16">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="17">
+    <cfRule type="expression" dxfId="9" priority="17">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U10">
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+  <conditionalFormatting sqref="U2:V8">
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>AND($X2&lt;&gt;"",OR($AE2="Yes",$AF2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
-      <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>OR($AE2="Yes",$AF2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="7">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>AND($AE2&lt;&gt;"Yes",$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD3">
-    <cfRule type="expression" dxfId="6" priority="23">
+  <conditionalFormatting sqref="U2:AE8">
+    <cfRule type="expression" dxfId="5" priority="23">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD10">
-    <cfRule type="expression" dxfId="5" priority="24">
+    <cfRule type="expression" dxfId="4" priority="24">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U4:AD10">
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>AND($J4&lt;&gt;"",$J4&lt;&gt;"Unclear due to correction")</formula>
+  <conditionalFormatting sqref="W2:W8">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V10">
-    <cfRule type="expression" dxfId="3" priority="2">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+  <conditionalFormatting sqref="X2:X8">
+    <cfRule type="expression" dxfId="2" priority="5">
+      <formula>AND($Y2="Yes",$Z2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="6">
+      <formula>$Y2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W10">
-    <cfRule type="expression" dxfId="2" priority="5">
-      <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="6">
-      <formula>$X2=""</formula>
+  <conditionalFormatting sqref="AC2:AC8">
+    <cfRule type="expression" dxfId="0" priority="8">
+      <formula>AND(OR($AC2&lt;&gt;"",$AD2&lt;&gt;""),$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB10">
-    <cfRule type="expression" dxfId="0" priority="8">
-      <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE10" xr:uid="{391A4C10-5B0F-402B-8464-4EEC91AC5A03}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF8" xr:uid="{391A4C10-5B0F-402B-8464-4EEC91AC5A03}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -31853,102 +32089,108 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="17">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{246E7149-FC3E-4D3D-B649-B6C9803D54B6}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$I$2:$I$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V8</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7CA901CC-B0BF-4EFF-9CE5-C40F35187D85}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D10</xm:sqref>
+          <xm:sqref>D2:D8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3E19E73C-F952-43EE-A079-9D2400972989}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E10</xm:sqref>
+          <xm:sqref>E2:E8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{293A8F56-2529-4C47-96E1-86E4BC2930F0}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$C$2:$C$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F10</xm:sqref>
+          <xm:sqref>F2:F8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AAA00612-90F2-4A7F-9390-249EC4D6BF80}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H10</xm:sqref>
+          <xm:sqref>H2:H8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2839770A-CBF2-4EF2-8A7F-3DC203AF0C8B}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$E$2:$E$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L10</xm:sqref>
+          <xm:sqref>L2:L8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0F260625-9D97-4F1F-B421-9B776984B36E}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$F$2:$F$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M10</xm:sqref>
+          <xm:sqref>M2:M8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{850C9034-2256-433A-A146-3DBB8A75218E}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$G$2:$G$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P10</xm:sqref>
+          <xm:sqref>P2:P8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{10DBC2F6-00D3-45E4-84B6-26151B4E6759}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$H$2:$H$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>U2:U10</xm:sqref>
+          <xm:sqref>U2:U8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{36853871-AAD7-4A3D-A18D-7D95F2CB95A6}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>V2:V10</xm:sqref>
+          <xm:sqref>W2:W8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29DDF3D7-101B-4521-B31F-E74E763BB5CE}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X10</xm:sqref>
+          <xm:sqref>Y2:Y8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{95249A93-C388-46D9-BE36-719E3D492F71}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W10</xm:sqref>
+          <xm:sqref>X2:X8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D05037A2-BC11-495A-9507-15F98759A6D3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y10</xm:sqref>
+          <xm:sqref>Z2:Z8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EA9A518-328A-41AD-97EA-1C41157F519E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Z2:Z10</xm:sqref>
+          <xm:sqref>AA2:AA8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4420CCB0-19B4-4FA8-B13B-B2C016107235}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AC2:AC10</xm:sqref>
+          <xm:sqref>AD2:AD8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7495220C-4B9E-473D-B45B-65B5E12E5DE0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AD2:AD10</xm:sqref>
+          <xm:sqref>AE2:AE8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6DB31ECE-088B-40E5-933F-F8F92C7F0360}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2:AB10</xm:sqref>
+          <xm:sqref>AC2:AC8</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -32126,13 +32368,13 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715E845E-DEC1-4CA3-83F1-8C5615D35CC4}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>337</v>
       </c>
@@ -32158,34 +32400,37 @@
         <v>527</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>498</v>
       </c>
@@ -32211,31 +32456,34 @@
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>499</v>
+        <v>903</v>
       </c>
       <c r="J3" t="s">
+        <v>499</v>
+      </c>
+      <c r="K3" t="s">
         <v>4</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>538</v>
       </c>
-      <c r="L3" t="s">
-        <v>499</v>
-      </c>
       <c r="M3" t="s">
+        <v>499</v>
+      </c>
+      <c r="N3" t="s">
         <v>539</v>
       </c>
-      <c r="N3" t="s">
-        <v>499</v>
-      </c>
       <c r="O3" t="s">
+        <v>499</v>
+      </c>
+      <c r="P3" t="s">
         <v>540</v>
       </c>
-      <c r="P3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>501</v>
       </c>
@@ -32261,31 +32509,34 @@
         <v>544</v>
       </c>
       <c r="I4" t="s">
+        <v>904</v>
+      </c>
+      <c r="J4" t="s">
         <v>506</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>544</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>861</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>506</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>546</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>506</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>547</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>505</v>
       </c>
@@ -32304,17 +32555,20 @@
       <c r="F5" t="s">
         <v>550</v>
       </c>
-      <c r="K5" t="s">
+      <c r="I5" t="s">
+        <v>905</v>
+      </c>
+      <c r="L5" t="s">
         <v>545</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>551</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>508</v>
       </c>
@@ -32327,14 +32581,14 @@
       <c r="E6" t="s">
         <v>554</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>555</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>510</v>
       </c>
@@ -32344,11 +32598,11 @@
       <c r="E7" t="s">
         <v>558</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>512</v>
       </c>
@@ -32358,11 +32612,11 @@
       <c r="E8" t="s">
         <v>560</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>347</v>
       </c>
@@ -32372,11 +32626,11 @@
       <c r="E9" t="s">
         <v>562</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>514</v>
       </c>
@@ -32386,44 +32640,44 @@
       <c r="E10" t="s">
         <v>564</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>590</v>
       </c>
       <c r="E11" t="s">
         <v>566</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N11" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>515</v>
       </c>
       <c r="E12" t="s">
         <v>568</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>567</v>
       </c>
       <c r="E13" t="s">
         <v>593</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>516</v>
       </c>
@@ -32431,12 +32685,12 @@
         <v>569</v>
       </c>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>518</v>
       </c>
@@ -32474,7 +32728,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3AC0717-40A1-483E-AF68-5D765FCE5A25}">
-  <dimension ref="A1:AE87"/>
+  <dimension ref="A1:AE97"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -37225,112 +37479,149 @@
       <c r="R87" s="7"/>
       <c r="S87" s="7"/>
     </row>
+    <row r="88" spans="1:30">
+      <c r="F88">
+        <f>COUNTIF(F2:F84,"Yes")</f>
+        <v>9</v>
+      </c>
+      <c r="R88" s="7"/>
+      <c r="S88" s="7"/>
+    </row>
+    <row r="89" spans="1:30">
+      <c r="R89" s="7"/>
+      <c r="S89" s="7"/>
+    </row>
+    <row r="90" spans="1:30">
+      <c r="R90" s="7"/>
+      <c r="S90" s="7"/>
+    </row>
+    <row r="91" spans="1:30">
+      <c r="R91" s="7"/>
+      <c r="S91" s="7"/>
+    </row>
+    <row r="92" spans="1:30">
+      <c r="R92" s="7"/>
+      <c r="S92" s="7"/>
+    </row>
+    <row r="96" spans="1:30">
+      <c r="AD96">
+        <f>COUNTIF(AD2:AD84, "Yes")</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="30:30">
+      <c r="AD97">
+        <f>COUNTIF(AD2:AD84,"Yes")/COUNTA(AD1:AD84)</f>
+        <v>0.33734939759036142</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:AE1" xr:uid="{B3AC0717-40A1-483E-AF68-5D765FCE5A25}"/>
   <conditionalFormatting sqref="G2:G84">
-    <cfRule type="expression" dxfId="324" priority="27">
+    <cfRule type="expression" dxfId="322" priority="27">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="323" priority="28">
+    <cfRule type="expression" dxfId="321" priority="28">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L84 O2:P84">
-    <cfRule type="expression" dxfId="322" priority="25">
+    <cfRule type="expression" dxfId="320" priority="25">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="321" priority="26">
+    <cfRule type="expression" dxfId="319" priority="26">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P84">
-    <cfRule type="expression" dxfId="320" priority="24">
+    <cfRule type="expression" dxfId="318" priority="24">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K84">
-    <cfRule type="expression" dxfId="319" priority="19">
+    <cfRule type="expression" dxfId="317" priority="19">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N84">
-    <cfRule type="expression" dxfId="318" priority="15">
+    <cfRule type="expression" dxfId="316" priority="15">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="317" priority="16">
+    <cfRule type="expression" dxfId="315" priority="16">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="316" priority="17">
+    <cfRule type="expression" dxfId="314" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="315" priority="18">
+    <cfRule type="expression" dxfId="313" priority="18">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O84">
-    <cfRule type="expression" dxfId="314" priority="20">
+    <cfRule type="expression" dxfId="312" priority="20">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AD2,6)&lt;&gt;"strict",$AC2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:S84 R85:S87">
-    <cfRule type="expression" dxfId="313" priority="21">
+  <conditionalFormatting sqref="Q2:S84 R85:S92">
+    <cfRule type="expression" dxfId="311" priority="21">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="312" priority="22">
+    <cfRule type="expression" dxfId="310" priority="22">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="311" priority="23">
+    <cfRule type="expression" dxfId="309" priority="23">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T84">
-    <cfRule type="expression" dxfId="310" priority="9">
+    <cfRule type="expression" dxfId="308" priority="9">
       <formula>AND($V2&lt;&gt;"",OR($AC2="Yes",$AD2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="309" priority="10">
+    <cfRule type="expression" dxfId="307" priority="10">
       <formula>OR($AC2="Yes",$AD2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="308" priority="13">
+    <cfRule type="expression" dxfId="306" priority="13">
       <formula>AND($AC2&lt;&gt;"Yes",$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:AC8 T10:AC33">
-    <cfRule type="expression" dxfId="307" priority="29">
+    <cfRule type="expression" dxfId="305" priority="29">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:AC8 T10:AC84">
-    <cfRule type="expression" dxfId="306" priority="30">
+    <cfRule type="expression" dxfId="304" priority="30">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T9:AC9">
-    <cfRule type="expression" dxfId="305" priority="2">
+    <cfRule type="expression" dxfId="303" priority="2">
       <formula>AND($I9&lt;&gt;"",$I9&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="304" priority="3">
+    <cfRule type="expression" dxfId="302" priority="3">
       <formula>OR($I9="",$I9="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T34:AC84">
-    <cfRule type="expression" dxfId="303" priority="1">
+    <cfRule type="expression" dxfId="301" priority="1">
       <formula>AND($I34&lt;&gt;"",$I34&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U84">
-    <cfRule type="expression" dxfId="302" priority="8">
+    <cfRule type="expression" dxfId="300" priority="8">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$W2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V84">
-    <cfRule type="expression" dxfId="301" priority="11">
+    <cfRule type="expression" dxfId="299" priority="11">
       <formula>AND($W2="Yes",$X2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="300" priority="12">
+    <cfRule type="expression" dxfId="298" priority="12">
       <formula>$W2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA84">
-    <cfRule type="expression" dxfId="299" priority="14">
+    <cfRule type="expression" dxfId="297" priority="14">
       <formula>AND(OR($AA2&lt;&gt;"",$AB2&lt;&gt;""),$AC2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37395,49 +37686,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{547ED45D-8063-4948-B7D4-37BB4BB98DFC}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U8 U10:U84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{23CAB4D0-E0B3-4A6D-877C-BA660EA5A360}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W8 W10:W84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D11A3614-A87A-41BD-9C2E-9F019E5EF4EA}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V8 V10:V84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F69B3807-187A-40B3-A8C1-1E9C915640F3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X8 X10:X84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8C67EF72-93B9-41B3-B3D6-A61FAB0094B3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y8 Y10:Y84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9AFA127-AB30-4FAA-A655-F2589EA18DC7}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB8 AB10:AB84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3940B2ED-1FDB-4C01-ABD7-AFA7AE557BC9}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC8 AC10:AC84</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{76576052-5BE2-45C2-8DD6-FDE52F36402C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA8 AA10:AA84</xm:sqref>
         </x14:dataValidation>
@@ -37449,7 +37740,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{565FD1AB-3775-434E-83DD-EAB1AE1BE582}">
-  <dimension ref="A1:AE99"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:31" s="2" customFormat="1">
@@ -41005,126 +41296,150 @@
       <c r="S99" s="7"/>
       <c r="T99" s="7"/>
     </row>
+    <row r="100" spans="19:20">
+      <c r="S100" s="7"/>
+      <c r="T100" s="7"/>
+    </row>
+    <row r="101" spans="19:20">
+      <c r="S101" s="7"/>
+      <c r="T101" s="7"/>
+    </row>
+    <row r="102" spans="19:20">
+      <c r="S102" s="7"/>
+      <c r="T102" s="7"/>
+    </row>
+    <row r="103" spans="19:20">
+      <c r="S103" s="7"/>
+      <c r="T103" s="7"/>
+    </row>
+    <row r="104" spans="19:20">
+      <c r="S104" s="7"/>
+      <c r="T104" s="7"/>
+    </row>
+    <row r="105" spans="19:20">
+      <c r="S105" s="7"/>
+      <c r="T105" s="7"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D63:F63"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:G44">
-    <cfRule type="expression" dxfId="298" priority="26">
+    <cfRule type="expression" dxfId="296" priority="26">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="297" priority="27">
+    <cfRule type="expression" dxfId="295" priority="27">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L44 O2:P44">
-    <cfRule type="expression" dxfId="296" priority="24">
+    <cfRule type="expression" dxfId="294" priority="24">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="295" priority="25">
+    <cfRule type="expression" dxfId="293" priority="25">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P44">
-    <cfRule type="expression" dxfId="294" priority="23">
+    <cfRule type="expression" dxfId="292" priority="23">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K44">
-    <cfRule type="expression" dxfId="293" priority="18">
+    <cfRule type="expression" dxfId="291" priority="18">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N44">
-    <cfRule type="expression" dxfId="292" priority="14">
+    <cfRule type="expression" dxfId="290" priority="14">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="291" priority="15">
+    <cfRule type="expression" dxfId="289" priority="15">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="290" priority="16">
+    <cfRule type="expression" dxfId="288" priority="16">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="289" priority="17">
+    <cfRule type="expression" dxfId="287" priority="17">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O44">
-    <cfRule type="expression" dxfId="288" priority="19">
+    <cfRule type="expression" dxfId="286" priority="19">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q44">
-    <cfRule type="expression" dxfId="287" priority="1">
+    <cfRule type="expression" dxfId="285" priority="1">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="286" priority="2">
+    <cfRule type="expression" dxfId="284" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="285" priority="3">
+    <cfRule type="expression" dxfId="283" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:T44 S45:T99">
-    <cfRule type="expression" dxfId="284" priority="20">
+  <conditionalFormatting sqref="R2:T44 S45:T105">
+    <cfRule type="expression" dxfId="282" priority="20">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="283" priority="21">
+    <cfRule type="expression" dxfId="281" priority="21">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="282" priority="22">
+    <cfRule type="expression" dxfId="280" priority="22">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U44">
-    <cfRule type="expression" dxfId="281" priority="8">
+    <cfRule type="expression" dxfId="279" priority="8">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="280" priority="9">
+    <cfRule type="expression" dxfId="278" priority="9">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="279" priority="12">
+    <cfRule type="expression" dxfId="277" priority="12">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD3 U5:AD16">
-    <cfRule type="expression" dxfId="278" priority="28">
+    <cfRule type="expression" dxfId="276" priority="28">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD3 U5:AD44">
-    <cfRule type="expression" dxfId="277" priority="29">
+    <cfRule type="expression" dxfId="275" priority="29">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U4:AD4">
-    <cfRule type="expression" dxfId="276" priority="5">
+    <cfRule type="expression" dxfId="274" priority="5">
       <formula>AND($I4&lt;&gt;"",$I4&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="275" priority="6">
+    <cfRule type="expression" dxfId="273" priority="6">
       <formula>OR($I4="",$I4="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U17:AD44">
-    <cfRule type="expression" dxfId="274" priority="4">
+    <cfRule type="expression" dxfId="272" priority="4">
       <formula>AND($I17&lt;&gt;"",$I17&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V44">
-    <cfRule type="expression" dxfId="273" priority="7">
+    <cfRule type="expression" dxfId="271" priority="7">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W44">
-    <cfRule type="expression" dxfId="272" priority="10">
+    <cfRule type="expression" dxfId="270" priority="10">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="271" priority="11">
+    <cfRule type="expression" dxfId="269" priority="11">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB44">
-    <cfRule type="expression" dxfId="270" priority="13">
+    <cfRule type="expression" dxfId="268" priority="13">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -41189,49 +41504,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{4D1D3608-74F0-4661-B1BE-F44D127E4510}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V3 V5:V44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6A9F8883-AA6D-497D-A4B1-A765E01EEFDB}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X3 X5:X44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6FD8EA49-E976-4FAA-B4E6-EB78C021F718}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W3 W5:W44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2D7B063E-C603-4BDC-B89E-B1A74C8210F7}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y3 Y5:Y44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{415147F1-6572-414A-BBA5-D3AE2FFD48D4}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z3 Z5:Z44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EBE4232B-6E4A-4F33-B4D9-8DDFB7B4FCFF}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC3 AC5:AC44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B73BF7B4-5029-4761-B24C-4770463AE91D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD3 AD5:AD44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{59371608-E7BB-48B7-878C-0045FC405BD2}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB3 AB5:AB44</xm:sqref>
         </x14:dataValidation>
@@ -42983,113 +43298,113 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G25">
-    <cfRule type="expression" dxfId="269" priority="24">
+    <cfRule type="expression" dxfId="267" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="268" priority="25">
+    <cfRule type="expression" dxfId="266" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L25 O2:P25">
-    <cfRule type="expression" dxfId="267" priority="22">
+    <cfRule type="expression" dxfId="265" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="266" priority="23">
+    <cfRule type="expression" dxfId="264" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P25">
-    <cfRule type="expression" dxfId="265" priority="21">
+    <cfRule type="expression" dxfId="263" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K25">
-    <cfRule type="expression" dxfId="264" priority="16">
+    <cfRule type="expression" dxfId="262" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N25">
-    <cfRule type="expression" dxfId="263" priority="12">
+    <cfRule type="expression" dxfId="261" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="262" priority="13">
+    <cfRule type="expression" dxfId="260" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="261" priority="14">
+    <cfRule type="expression" dxfId="259" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="260" priority="15">
+    <cfRule type="expression" dxfId="258" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O25">
-    <cfRule type="expression" dxfId="259" priority="17">
+    <cfRule type="expression" dxfId="257" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q25">
-    <cfRule type="expression" dxfId="258" priority="2">
+    <cfRule type="expression" dxfId="256" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="257" priority="3">
+    <cfRule type="expression" dxfId="255" priority="3">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="256" priority="4">
+    <cfRule type="expression" dxfId="254" priority="4">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T25">
-    <cfRule type="expression" dxfId="255" priority="18">
+    <cfRule type="expression" dxfId="253" priority="18">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="254" priority="19">
+    <cfRule type="expression" dxfId="252" priority="19">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="253" priority="20">
+    <cfRule type="expression" dxfId="251" priority="20">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U25">
-    <cfRule type="expression" dxfId="252" priority="6">
+    <cfRule type="expression" dxfId="250" priority="6">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="251" priority="7">
+    <cfRule type="expression" dxfId="249" priority="7">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="250" priority="10">
+    <cfRule type="expression" dxfId="248" priority="10">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD9">
-    <cfRule type="expression" dxfId="249" priority="26">
+    <cfRule type="expression" dxfId="247" priority="26">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD25">
-    <cfRule type="expression" dxfId="248" priority="27">
+    <cfRule type="expression" dxfId="246" priority="27">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:AD25">
-    <cfRule type="expression" dxfId="247" priority="1">
+    <cfRule type="expression" dxfId="245" priority="1">
       <formula>AND($I10&lt;&gt;"",$I10&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V25">
-    <cfRule type="expression" dxfId="246" priority="5">
+    <cfRule type="expression" dxfId="244" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W25">
-    <cfRule type="expression" dxfId="245" priority="8">
+    <cfRule type="expression" dxfId="243" priority="8">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="244" priority="9">
+    <cfRule type="expression" dxfId="242" priority="9">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB25">
-    <cfRule type="expression" dxfId="243" priority="11">
+    <cfRule type="expression" dxfId="241" priority="11">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43106,49 +43421,49 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B3B488D-BDE9-4F73-BF3F-C2B244F9BC20}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{21E70722-7975-4877-81D6-9E37321445F5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F64F10FF-F218-4595-B7C7-B90F4A764D4A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{727AE634-00C0-405E-B052-676D8C55DD5D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9A459BC9-9A3A-4B46-9B36-24A0426D62FE}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{55D2F18A-030E-4F89-8696-42FFC083A5F0}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C326189E-8823-4C9B-A075-C39E206CF372}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X25</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{7228389E-8210-4DA4-8229-1CB537C86A67}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V25</xm:sqref>
         </x14:dataValidation>
@@ -43208,7 +43523,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8729C93E-07C3-4619-ABD1-D814719CE37B}">
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:31" s="2" customFormat="1">
@@ -43494,119 +43809,139 @@
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
     </row>
+    <row r="17" spans="18:19">
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+    </row>
+    <row r="18" spans="18:19">
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+    </row>
+    <row r="19" spans="18:19">
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+    </row>
+    <row r="20" spans="18:19">
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+    </row>
+    <row r="21" spans="18:19">
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="G2">
-    <cfRule type="expression" dxfId="242" priority="24">
+    <cfRule type="expression" dxfId="240" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="241" priority="25">
+    <cfRule type="expression" dxfId="239" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L2 O2:P2">
-    <cfRule type="expression" dxfId="240" priority="22">
+    <cfRule type="expression" dxfId="238" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="239" priority="23">
+    <cfRule type="expression" dxfId="237" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P2">
-    <cfRule type="expression" dxfId="238" priority="21">
+    <cfRule type="expression" dxfId="236" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2">
-    <cfRule type="expression" dxfId="237" priority="16">
+    <cfRule type="expression" dxfId="235" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N2">
-    <cfRule type="expression" dxfId="236" priority="12">
+    <cfRule type="expression" dxfId="234" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="235" priority="13">
+    <cfRule type="expression" dxfId="233" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="234" priority="14">
+    <cfRule type="expression" dxfId="232" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="233" priority="15">
+    <cfRule type="expression" dxfId="231" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2">
-    <cfRule type="expression" dxfId="232" priority="17">
+    <cfRule type="expression" dxfId="230" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="expression" dxfId="231" priority="1">
+    <cfRule type="expression" dxfId="229" priority="1">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="230" priority="2">
+    <cfRule type="expression" dxfId="228" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="229" priority="3">
+    <cfRule type="expression" dxfId="227" priority="3">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R3:S16">
-    <cfRule type="expression" dxfId="228" priority="30">
+  <conditionalFormatting sqref="R3:S21">
+    <cfRule type="expression" dxfId="226" priority="30">
       <formula>AND(AND(LEFT($I3,3)="Sub", RIGHT($I3,4)&lt;&gt;"Form"),$S3&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="227" priority="31">
+    <cfRule type="expression" dxfId="225" priority="31">
       <formula>AND(AND(LEFT($I3,3)="Sub", RIGHT($I3,4)&lt;&gt;"Form"),$S3="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="226" priority="32">
+    <cfRule type="expression" dxfId="224" priority="32">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T2">
-    <cfRule type="expression" dxfId="225" priority="18">
+    <cfRule type="expression" dxfId="223" priority="18">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="224" priority="19">
+    <cfRule type="expression" dxfId="222" priority="19">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="223" priority="20">
+    <cfRule type="expression" dxfId="221" priority="20">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="expression" dxfId="222" priority="6">
+    <cfRule type="expression" dxfId="220" priority="6">
       <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="221" priority="7">
+    <cfRule type="expression" dxfId="219" priority="7">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="220" priority="10">
+    <cfRule type="expression" dxfId="218" priority="10">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD2">
-    <cfRule type="expression" dxfId="219" priority="4">
+    <cfRule type="expression" dxfId="217" priority="4">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="218" priority="26">
+    <cfRule type="expression" dxfId="216" priority="26">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2">
-    <cfRule type="expression" dxfId="217" priority="5">
+    <cfRule type="expression" dxfId="215" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2">
-    <cfRule type="expression" dxfId="216" priority="8">
+    <cfRule type="expression" dxfId="214" priority="8">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="215" priority="9">
+    <cfRule type="expression" dxfId="213" priority="9">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2">
-    <cfRule type="expression" dxfId="214" priority="11">
+    <cfRule type="expression" dxfId="212" priority="11">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43622,49 +43957,49 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A031E94E-8C5E-4F98-9D8F-B154480722E3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1DE6C178-27BF-4A62-AC66-23D2C28DD50F}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1BF0CAD9-7156-4435-90EE-D106D1E1627B}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4C136CE7-A3DF-48A2-B6D5-49FCE2426B59}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F79D9717-A777-43AC-A526-2158BF913D57}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F87823B1-0E87-4D10-929E-2E42E298FBB3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0F064A1D-BD39-4FA1-BA41-8E9393163BB5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{0AD67DB4-DFAA-462B-8855-1A611024FC73}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2</xm:sqref>
         </x14:dataValidation>
@@ -44803,102 +45138,102 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G15">
-    <cfRule type="expression" dxfId="213" priority="24">
+    <cfRule type="expression" dxfId="211" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="212" priority="25">
+    <cfRule type="expression" dxfId="210" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L15 O2:P15">
-    <cfRule type="expression" dxfId="211" priority="22">
+    <cfRule type="expression" dxfId="209" priority="22">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="210" priority="23">
+    <cfRule type="expression" dxfId="208" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P15">
-    <cfRule type="expression" dxfId="209" priority="21">
+    <cfRule type="expression" dxfId="207" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K15">
-    <cfRule type="expression" dxfId="208" priority="16">
+    <cfRule type="expression" dxfId="206" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N15">
-    <cfRule type="expression" dxfId="207" priority="12">
+    <cfRule type="expression" dxfId="205" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="206" priority="13">
+    <cfRule type="expression" dxfId="204" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="205" priority="14">
+    <cfRule type="expression" dxfId="203" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="204" priority="15">
+    <cfRule type="expression" dxfId="202" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O15">
-    <cfRule type="expression" dxfId="203" priority="17">
+    <cfRule type="expression" dxfId="201" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AG2,6)&lt;&gt;"strict",$AF2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:V15">
-    <cfRule type="expression" dxfId="202" priority="1">
+    <cfRule type="expression" dxfId="200" priority="1">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="201" priority="2">
+    <cfRule type="expression" dxfId="199" priority="2">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="200" priority="3">
+    <cfRule type="expression" dxfId="198" priority="3">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W15">
-    <cfRule type="expression" dxfId="199" priority="6">
+    <cfRule type="expression" dxfId="197" priority="6">
       <formula>AND($Y2&lt;&gt;"",OR($AF2="Yes",$AG2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="198" priority="7">
+    <cfRule type="expression" dxfId="196" priority="7">
       <formula>OR($AF2="Yes",$AG2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="197" priority="10">
+    <cfRule type="expression" dxfId="195" priority="10">
       <formula>AND($AF2&lt;&gt;"Yes",$AG2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AF5">
-    <cfRule type="expression" dxfId="196" priority="26">
+    <cfRule type="expression" dxfId="194" priority="26">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:AF15">
-    <cfRule type="expression" dxfId="195" priority="27">
+    <cfRule type="expression" dxfId="193" priority="27">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W6:AF15">
-    <cfRule type="expression" dxfId="194" priority="4">
+    <cfRule type="expression" dxfId="192" priority="4">
       <formula>AND($I6&lt;&gt;"",$I6&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X15">
-    <cfRule type="expression" dxfId="193" priority="5">
+    <cfRule type="expression" dxfId="191" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$Z2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y15">
-    <cfRule type="expression" dxfId="192" priority="8">
+    <cfRule type="expression" dxfId="190" priority="8">
       <formula>AND($Z2="Yes",$AA2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="191" priority="9">
+    <cfRule type="expression" dxfId="189" priority="9">
       <formula>$Z2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD15">
-    <cfRule type="expression" dxfId="190" priority="11">
+    <cfRule type="expression" dxfId="188" priority="11">
       <formula>AND(OR($AD2&lt;&gt;"",$AE2&lt;&gt;""),$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -44963,49 +45298,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{D3ACA8E1-DE26-4298-A200-57FC2372AFDE}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ACCE3589-975F-44CD-8E60-1BBE702DE85D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D404A15-38BC-4CA1-9D84-B92ACA201844}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF52845B-DB3E-4FC8-8519-FA91C74CD099}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FDA7B10C-F141-4C26-AFED-9E1DD66D0693}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D5B5CFBB-E105-4FAD-B38B-7E8EB453FF08}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AE2:AE15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{63B03666-1F95-4C6A-827E-2EAD2DDECFB3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AF2:AF15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{60B4CD65-2332-438F-BD9D-067F17073FAD}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD15</xm:sqref>
         </x14:dataValidation>
@@ -45017,10 +45352,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9936908C-36BB-4003-BA0A-490D07349575}">
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AF30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="10.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="2" customFormat="1">
+    <row r="1" spans="1:32" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -45085,37 +45423,40 @@
         <v>527</v>
       </c>
       <c r="V1" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="29">
+    <row r="2" spans="1:32" ht="29">
       <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
@@ -45165,22 +45506,25 @@
       <c r="U2" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V2" s="7"/>
+      <c r="V2" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
-      <c r="Y2" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
-      <c r="AE2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" ht="29">
+      <c r="AE2" s="7"/>
+      <c r="AF2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="29">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -45230,22 +45574,25 @@
       <c r="U3" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V3" s="7"/>
+      <c r="V3" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
-      <c r="Y3" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
-      <c r="AE3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" ht="58">
+      <c r="AE3" s="7"/>
+      <c r="AF3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" ht="58">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -45285,22 +45632,25 @@
       <c r="U4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="V4" s="7"/>
+      <c r="V4" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
-      <c r="Y4" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
-      <c r="AE4" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" ht="58">
+      <c r="AE4" s="7"/>
+      <c r="AF4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="58">
       <c r="A5" s="1" t="s">
         <v>56</v>
       </c>
@@ -45340,22 +45690,25 @@
       <c r="U5" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V5" s="7"/>
+      <c r="V5" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-      <c r="Y5" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
-      <c r="AE5" t="s">
+      <c r="AE5" s="7"/>
+      <c r="AF5" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="43.5">
+    <row r="6" spans="1:32" ht="43.5">
       <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
@@ -45407,22 +45760,25 @@
       <c r="U6" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V6" s="7"/>
+      <c r="V6" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-      <c r="Y6" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
-      <c r="AE6" t="s">
+      <c r="AE6" s="7"/>
+      <c r="AF6" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="72.5">
+    <row r="7" spans="1:32" ht="72.5">
       <c r="A7" s="1" t="s">
         <v>98</v>
       </c>
@@ -45436,7 +45792,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>553</v>
@@ -45460,22 +45816,25 @@
       <c r="U7" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V7" s="7"/>
+      <c r="V7" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
-      <c r="Y7" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA7" s="7"/>
       <c r="AB7" s="7"/>
       <c r="AC7" s="7"/>
       <c r="AD7" s="7"/>
-      <c r="AE7" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="43.5">
+      <c r="AE7" s="7"/>
+      <c r="AF7" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="43.5">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -45489,7 +45848,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>553</v>
@@ -45513,22 +45872,25 @@
       <c r="U8" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V8" s="7"/>
+      <c r="V8" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
-      <c r="Y8" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA8" s="7"/>
       <c r="AB8" s="7"/>
       <c r="AC8" s="7"/>
       <c r="AD8" s="7"/>
-      <c r="AE8" t="s">
+      <c r="AE8" s="7"/>
+      <c r="AF8" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="29">
+    <row r="9" spans="1:32" ht="29">
       <c r="A9" s="1" t="s">
         <v>165</v>
       </c>
@@ -45566,22 +45928,25 @@
       <c r="U9" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V9" s="7"/>
+      <c r="V9" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA9" s="7"/>
       <c r="AB9" s="7"/>
       <c r="AC9" s="7"/>
       <c r="AD9" s="7"/>
-      <c r="AE9" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="29">
+      <c r="AE9" s="7"/>
+      <c r="AF9" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" ht="29">
       <c r="A10" s="1" t="s">
         <v>195</v>
       </c>
@@ -45621,22 +45986,25 @@
       <c r="U10" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V10" s="7"/>
+      <c r="V10" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
-      <c r="Y10" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA10" s="7"/>
       <c r="AB10" s="7"/>
       <c r="AC10" s="7"/>
       <c r="AD10" s="7"/>
-      <c r="AE10" t="s">
+      <c r="AE10" s="7"/>
+      <c r="AF10" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="101.5">
+    <row r="11" spans="1:32" ht="101.5">
       <c r="A11" s="1" t="s">
         <v>215</v>
       </c>
@@ -45688,22 +46056,25 @@
       <c r="U11" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V11" s="7"/>
+      <c r="V11" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-      <c r="Y11" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA11" s="7"/>
       <c r="AB11" s="7"/>
       <c r="AC11" s="7"/>
       <c r="AD11" s="7"/>
-      <c r="AE11" t="s">
+      <c r="AE11" s="7"/>
+      <c r="AF11" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="43.5">
+    <row r="12" spans="1:32" ht="43.5">
       <c r="A12" s="1" t="s">
         <v>219</v>
       </c>
@@ -45743,39 +46114,42 @@
       <c r="U12" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V12" s="7"/>
+      <c r="V12" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-      <c r="Y12" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA12" s="7"/>
       <c r="AB12" s="7"/>
       <c r="AC12" s="7"/>
       <c r="AD12" s="7"/>
-      <c r="AE12" t="s">
+      <c r="AE12" s="7"/>
+      <c r="AF12" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="72.5">
+    <row r="13" spans="1:32" ht="87">
       <c r="A13" s="1" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>443</v>
+        <v>706</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>444</v>
+        <v>707</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" t="s">
-        <v>900</v>
+        <v>777</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="I13" s="7">
         <v>0</v>
@@ -45784,19 +46158,19 @@
         <v>1</v>
       </c>
       <c r="K13" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>541</v>
+        <v>564</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="8"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7">
-        <v>19277</v>
+        <v>903</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7" t="s">
@@ -45808,36 +46182,39 @@
       <c r="U13" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V13" s="7"/>
+      <c r="V13" s="7" t="s">
+        <v>903</v>
+      </c>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-      <c r="Y13" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA13" s="7"/>
       <c r="AB13" s="7"/>
       <c r="AC13" s="7"/>
       <c r="AD13" s="7"/>
-      <c r="AE13" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" ht="72.5">
+      <c r="AE13" s="7"/>
+      <c r="AF13" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" ht="29">
       <c r="A14" s="1" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>900</v>
+        <v>778</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>504</v>
@@ -45849,13 +46226,13 @@
         <v>1</v>
       </c>
       <c r="K14" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>541</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="8"/>
@@ -45873,60 +46250,65 @@
       <c r="U14" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V14" s="7"/>
+      <c r="V14" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-      <c r="Y14" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA14" s="7"/>
       <c r="AB14" s="7"/>
       <c r="AC14" s="7"/>
       <c r="AD14" s="7"/>
-      <c r="AE14" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" ht="87">
+      <c r="AE14" s="7"/>
+      <c r="AF14" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="116">
       <c r="A15" s="1" t="s">
-        <v>246</v>
+        <v>314</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>706</v>
+        <v>484</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>707</v>
+        <v>485</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="I15" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15" s="7">
-        <v>2</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>564</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="L15" s="7"/>
       <c r="M15" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="N15" s="7"/>
-      <c r="O15" s="8"/>
+        <v>536</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>747</v>
+      </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7">
-        <v>903</v>
+        <v>43</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7" t="s">
@@ -45938,36 +46320,39 @@
       <c r="U15" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V15" s="7"/>
+      <c r="V15" s="7" t="s">
+        <v>904</v>
+      </c>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-      <c r="Y15" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA15" s="7"/>
       <c r="AB15" s="7"/>
       <c r="AC15" s="7"/>
       <c r="AD15" s="7"/>
-      <c r="AE15" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" ht="29">
+      <c r="AE15" s="7"/>
+      <c r="AF15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="43.5">
       <c r="A16" s="1" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>504</v>
@@ -45979,7 +46364,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="7" t="s">
         <v>541</v>
@@ -46003,62 +46388,63 @@
       <c r="U16" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V16" s="7"/>
+      <c r="V16" s="7" t="s">
+        <v>905</v>
+      </c>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-      <c r="Y16" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA16" s="7"/>
       <c r="AB16" s="7"/>
       <c r="AC16" s="7"/>
       <c r="AD16" s="7"/>
-      <c r="AE16" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" ht="116">
+      <c r="AE16" s="7"/>
+      <c r="AF16" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="43.5">
       <c r="A17" s="1" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>504</v>
       </c>
       <c r="I17" s="7">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
         <v>1</v>
       </c>
-      <c r="J17" s="7">
-        <v>4</v>
-      </c>
       <c r="K17" s="7">
-        <v>17</v>
-      </c>
-      <c r="L17" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>541</v>
+      </c>
       <c r="M17" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>747</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N17" s="7"/>
+      <c r="O17" s="8"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7">
-        <v>43</v>
+        <v>19277</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7" t="s">
@@ -46070,60 +46456,65 @@
       <c r="U17" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V17" s="7"/>
+      <c r="V17" s="7" t="s">
+        <v>905</v>
+      </c>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-      <c r="Y17" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z17" s="7"/>
+      <c r="Y17" s="7"/>
+      <c r="Z17" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA17" s="7"/>
       <c r="AB17" s="7"/>
       <c r="AC17" s="7"/>
       <c r="AD17" s="7"/>
-      <c r="AE17" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" ht="43.5">
+      <c r="AE17" s="7"/>
+      <c r="AF17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="87">
       <c r="A18" s="1" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>504</v>
       </c>
       <c r="I18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" s="7">
-        <v>2</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>541</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="L18" s="7"/>
       <c r="M18" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="N18" s="7"/>
-      <c r="O18" s="8"/>
+        <v>536</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>757</v>
+      </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="7">
-        <v>19277</v>
+        <v>119</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7" t="s">
@@ -46135,283 +46526,267 @@
       <c r="U18" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="V18" s="7"/>
+      <c r="V18" s="7" t="s">
+        <v>905</v>
+      </c>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-      <c r="Y18" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z18" s="7"/>
+      <c r="Y18" s="7"/>
+      <c r="Z18" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="AA18" s="7"/>
       <c r="AB18" s="7"/>
       <c r="AC18" s="7"/>
       <c r="AD18" s="7"/>
-      <c r="AE18" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" ht="43.5">
-      <c r="A19" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" t="s">
-        <v>781</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="I19" s="7">
-        <v>0</v>
-      </c>
-      <c r="J19" s="7">
-        <v>1</v>
-      </c>
-      <c r="K19" s="7">
-        <v>2</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="N19" s="7"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7">
-        <v>19277</v>
-      </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="7"/>
-      <c r="AD19" s="7"/>
-      <c r="AE19" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" ht="87">
-      <c r="A20" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" t="s">
-        <v>782</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="I20" s="7">
-        <v>1</v>
-      </c>
-      <c r="J20" s="7">
-        <v>3</v>
-      </c>
-      <c r="K20" s="7">
-        <v>14</v>
-      </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>642</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>757</v>
-      </c>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7">
-        <v>119</v>
-      </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="U20" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="7"/>
-      <c r="AD20" s="7"/>
-      <c r="AE20" t="s">
+      <c r="AE18" s="7"/>
+      <c r="AF18" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
-      <c r="D23" t="s">
+    <row r="21" spans="1:32">
+      <c r="D21" t="s">
         <v>853</v>
       </c>
-      <c r="E23">
+      <c r="E21">
         <f>COUNTIF(U:U, "Harmonizing")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
-      <c r="D24" t="s">
+    <row r="22" spans="1:32">
+      <c r="D22" t="s">
         <v>854</v>
       </c>
-      <c r="E24">
+      <c r="E22">
         <f>COUNTIF(U:U, "Disharmonizing")</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31">
-      <c r="D25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32">
+      <c r="D23" t="s">
         <v>855</v>
       </c>
-      <c r="E25">
-        <f>E23/(E23+E24)</f>
-        <v>5.2631578947368418E-2</v>
+      <c r="E23">
+        <f>E21/(E21+E22)</f>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32">
+      <c r="E26" s="13" t="s">
+        <v>906</v>
+      </c>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="1:32">
+      <c r="E27" t="s">
+        <v>907</v>
+      </c>
+      <c r="F27" t="s">
+        <v>908</v>
+      </c>
+      <c r="G27" t="s">
+        <v>909</v>
+      </c>
+      <c r="H27" t="s">
+        <v>910</v>
+      </c>
+      <c r="I27" t="s">
+        <v>905</v>
+      </c>
+      <c r="J27" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32">
+      <c r="D28" t="s">
+        <v>853</v>
+      </c>
+      <c r="E28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward")</f>
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward")</f>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both")</f>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f>COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"both") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Harmonizing",$V$2:$V$18,"backward")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32">
+      <c r="D29" t="s">
+        <v>854</v>
+      </c>
+      <c r="E29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward")</f>
+        <v>5</v>
+      </c>
+      <c r="F29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>8</v>
+      </c>
+      <c r="G29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward")</f>
+        <v>8</v>
+      </c>
+      <c r="H29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>11</v>
+      </c>
+      <c r="I29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both")</f>
+        <v>3</v>
+      </c>
+      <c r="J29">
+        <f>COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"both") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"forward") + COUNTIFS($U$2:$U$18,"Disharmonizing",$V$2:$V$18,"backward")</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32">
+      <c r="D30" t="s">
+        <v>855</v>
+      </c>
+      <c r="E30">
+        <f t="shared" ref="E30:J30" si="0">E28/(E28+E29)</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H20">
-    <cfRule type="expression" dxfId="189" priority="21">
+  <mergeCells count="1">
+    <mergeCell ref="E26:J26"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H2:H18">
+    <cfRule type="expression" dxfId="187" priority="21">
       <formula>$J2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="188" priority="22">
+    <cfRule type="expression" dxfId="186" priority="22">
       <formula>$J2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:M20 P2:Q20">
-    <cfRule type="expression" dxfId="187" priority="19">
+  <conditionalFormatting sqref="I2:M18 P2:Q18">
+    <cfRule type="expression" dxfId="185" priority="19">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="186" priority="20">
+    <cfRule type="expression" dxfId="184" priority="20">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission",$J2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:Q20">
-    <cfRule type="expression" dxfId="185" priority="18">
+  <conditionalFormatting sqref="I2:Q18">
+    <cfRule type="expression" dxfId="183" priority="18">
       <formula>AND(OR($J2="Addition",$J2="Omission"), I2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L20">
-    <cfRule type="expression" dxfId="184" priority="13">
+  <conditionalFormatting sqref="L2:L18">
+    <cfRule type="expression" dxfId="182" priority="13">
       <formula>AND($L2&lt;&gt;"",$L2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O20">
-    <cfRule type="expression" dxfId="183" priority="9">
+  <conditionalFormatting sqref="N2:O18">
+    <cfRule type="expression" dxfId="181" priority="9">
       <formula>$O2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="182" priority="10">
+    <cfRule type="expression" dxfId="180" priority="10">
       <formula>$O2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="181" priority="11">
+    <cfRule type="expression" dxfId="179" priority="11">
       <formula>AND(OR($J2="Addition",$J2="Omission"), N2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="180" priority="12">
+    <cfRule type="expression" dxfId="178" priority="12">
       <formula>AND($J2&lt;&gt;"Addition",$J2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P20">
-    <cfRule type="expression" dxfId="179" priority="14">
-      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
+  <conditionalFormatting sqref="P2:P18">
+    <cfRule type="expression" dxfId="177" priority="14">
+      <formula>AND(OR($J2="Addition",$J2="Omission",$J2="Substitution - Word"),RIGHT($AF2,6)&lt;&gt;"strict",$AE2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:T20">
-    <cfRule type="expression" dxfId="178" priority="15">
+  <conditionalFormatting sqref="R2:T18">
+    <cfRule type="expression" dxfId="176" priority="15">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="177" priority="16">
+    <cfRule type="expression" dxfId="175" priority="16">
       <formula>AND(AND(LEFT($J2,3)="Sub", RIGHT($J2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="176" priority="17">
+    <cfRule type="expression" dxfId="174" priority="17">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U20">
-    <cfRule type="expression" dxfId="175" priority="3">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+  <conditionalFormatting sqref="U2:V18">
+    <cfRule type="expression" dxfId="173" priority="3">
+      <formula>AND($X2&lt;&gt;"",OR($AE2="Yes",$AF2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="174" priority="4">
-      <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
+    <cfRule type="expression" dxfId="172" priority="4">
+      <formula>OR($AE2="Yes",$AF2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="173" priority="7">
-      <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
+    <cfRule type="expression" dxfId="171" priority="7">
+      <formula>AND($AE2&lt;&gt;"Yes",$AF2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD7">
-    <cfRule type="expression" dxfId="172" priority="23">
+  <conditionalFormatting sqref="U2:AE18">
+    <cfRule type="expression" dxfId="170" priority="23">
       <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U2:AD20">
-    <cfRule type="expression" dxfId="171" priority="24">
+    <cfRule type="expression" dxfId="169" priority="24">
       <formula>OR($J2="",$J2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U8:AD20">
-    <cfRule type="expression" dxfId="170" priority="1">
-      <formula>AND($J8&lt;&gt;"",$J8&lt;&gt;"Unclear due to correction")</formula>
+  <conditionalFormatting sqref="W2:W18">
+    <cfRule type="expression" dxfId="168" priority="2">
+      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$Y2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V20">
-    <cfRule type="expression" dxfId="169" priority="2">
-      <formula>AND($J2&lt;&gt;"",$J2&lt;&gt;"Unclear due to correction",$X2="")</formula>
+  <conditionalFormatting sqref="X2:X18">
+    <cfRule type="expression" dxfId="167" priority="5">
+      <formula>AND($Y2="Yes",$Z2="")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="166" priority="6">
+      <formula>$Y2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W20">
-    <cfRule type="expression" dxfId="168" priority="5">
-      <formula>AND($X2="Yes",$Y2="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="167" priority="6">
-      <formula>$X2=""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB20">
-    <cfRule type="expression" dxfId="166" priority="8">
-      <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
+  <conditionalFormatting sqref="AC2:AC18">
+    <cfRule type="expression" dxfId="165" priority="8">
+      <formula>AND(OR($AC2&lt;&gt;"",$AD2&lt;&gt;""),$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE20" xr:uid="{003BA854-8E63-4D84-9444-33B6745AE2D5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF2:AF18" xr:uid="{003BA854-8E63-4D84-9444-33B6745AE2D5}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -46420,102 +46795,108 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="17">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{68EDBC33-543C-49B8-A3AC-77CFC8F3A7D7}">
+          <x14:formula1>
+            <xm:f>'Data Regularization'!$I$2:$I$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>V2:V18</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{97702572-5940-43E7-A376-026149B5FF1B}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D20</xm:sqref>
+          <xm:sqref>D2:D18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{892B13F5-A867-4F56-9686-FEE7EA50E926}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E20</xm:sqref>
+          <xm:sqref>E2:E18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FCD575B0-3FC1-4E83-980F-D488F104890B}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$C$2:$C$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F20</xm:sqref>
+          <xm:sqref>F2:F18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{32EEBD4A-5EE7-44C1-8C18-964C878BCBA3}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$D$2:$D$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H20</xm:sqref>
+          <xm:sqref>H2:H18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{105D60AA-763F-4885-A798-4C1FB61A1131}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$E$2:$E$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>L2:L20</xm:sqref>
+          <xm:sqref>L2:L18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C68AF3EA-FEBB-4E64-A219-747B44D6D22E}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$F$2:$F$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M20</xm:sqref>
+          <xm:sqref>M2:M18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B4829E6-9697-4B11-A017-983F9163903E}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$G$2:$G$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>P2:P20</xm:sqref>
+          <xm:sqref>P2:P18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BAB18D36-86C4-4C84-A077-E7BAFD8D268D}">
           <x14:formula1>
             <xm:f>'Data Regularization'!$H$2:$H$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>U2:U20</xm:sqref>
+          <xm:sqref>U2:U18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{A0426D7E-A79B-4F43-9F12-85DB22101188}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>V2:V20</xm:sqref>
+          <xm:sqref>W2:W18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A23FAC15-EEA9-45CD-A432-4921615F3E03}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>X2:X20</xm:sqref>
+          <xm:sqref>Y2:Y18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{862A06C4-B9A5-4A0C-ABB8-0FE4DD0FBD9E}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>W2:W20</xm:sqref>
+          <xm:sqref>X2:X18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B0FC5FBA-DB03-4C98-ABE8-4AFF4BD54223}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Y2:Y20</xm:sqref>
+          <xm:sqref>Z2:Z18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7F02B5F5-ECBD-44A9-9D20-2BE95A10EB61}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>Z2:Z20</xm:sqref>
+          <xm:sqref>AA2:AA18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9FB6F3E3-6D2A-4229-9AC9-C7D8D5B493FA}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AC2:AC20</xm:sqref>
+          <xm:sqref>AD2:AD18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE33B8AB-F0BD-46D2-948D-9EF54CA86569}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AD2:AD20</xm:sqref>
+          <xm:sqref>AE2:AE18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{131B3DB2-1C25-487E-8C9C-30D8CF0FD221}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>AB2:AB20</xm:sqref>
+          <xm:sqref>AC2:AC18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -49702,102 +50083,102 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G55">
-    <cfRule type="expression" dxfId="165" priority="21">
+    <cfRule type="expression" dxfId="164" priority="21">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="164" priority="22">
+    <cfRule type="expression" dxfId="163" priority="22">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L55 O2:P55">
-    <cfRule type="expression" dxfId="163" priority="19">
+    <cfRule type="expression" dxfId="162" priority="19">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="162" priority="20">
+    <cfRule type="expression" dxfId="161" priority="20">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P55">
-    <cfRule type="expression" dxfId="161" priority="18">
+    <cfRule type="expression" dxfId="160" priority="18">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K55">
-    <cfRule type="expression" dxfId="160" priority="13">
+    <cfRule type="expression" dxfId="159" priority="13">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N55">
-    <cfRule type="expression" dxfId="159" priority="9">
+    <cfRule type="expression" dxfId="158" priority="9">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="158" priority="10">
+    <cfRule type="expression" dxfId="157" priority="10">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="157" priority="11">
+    <cfRule type="expression" dxfId="156" priority="11">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="156" priority="12">
+    <cfRule type="expression" dxfId="155" priority="12">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O55">
-    <cfRule type="expression" dxfId="155" priority="14">
+    <cfRule type="expression" dxfId="154" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AD2,6)&lt;&gt;"strict",$AC2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:S55">
-    <cfRule type="expression" dxfId="154" priority="15">
+    <cfRule type="expression" dxfId="153" priority="15">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="16">
+    <cfRule type="expression" dxfId="152" priority="16">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$S2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="17">
+    <cfRule type="expression" dxfId="151" priority="17">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T55">
-    <cfRule type="expression" dxfId="151" priority="3">
+    <cfRule type="expression" dxfId="150" priority="3">
       <formula>AND($V2&lt;&gt;"",OR($AC2="Yes",$AD2&lt;&gt;""))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="4">
+    <cfRule type="expression" dxfId="149" priority="4">
       <formula>OR($AC2="Yes",$AD2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="7">
+    <cfRule type="expression" dxfId="148" priority="7">
       <formula>AND($AC2&lt;&gt;"Yes",$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:AC21">
-    <cfRule type="expression" dxfId="148" priority="23">
+    <cfRule type="expression" dxfId="147" priority="23">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:AC55">
-    <cfRule type="expression" dxfId="147" priority="24">
+    <cfRule type="expression" dxfId="146" priority="24">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T22:AC55">
-    <cfRule type="expression" dxfId="146" priority="1">
+    <cfRule type="expression" dxfId="145" priority="1">
       <formula>AND($I22&lt;&gt;"",$I22&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U55">
-    <cfRule type="expression" dxfId="145" priority="2">
+    <cfRule type="expression" dxfId="144" priority="2">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$W2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V55">
-    <cfRule type="expression" dxfId="144" priority="5">
+    <cfRule type="expression" dxfId="143" priority="5">
       <formula>AND($W2="Yes",$X2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="143" priority="6">
+    <cfRule type="expression" dxfId="142" priority="6">
       <formula>$W2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA55">
-    <cfRule type="expression" dxfId="142" priority="8">
+    <cfRule type="expression" dxfId="141" priority="8">
       <formula>AND(OR($AA2&lt;&gt;"",$AB2&lt;&gt;""),$AC2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49813,49 +50194,49 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="16">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0B9CEB8D-87E5-4F3D-9A23-6EF11B7433B3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AA2:AA55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D402A179-539E-46F4-92BD-DE0D1878175A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8ECFC381-17C6-49BD-B97A-ED13815ABFDA}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7ACA9E4A-7E7B-4072-825D-637D0C242874}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E27B3F50-8BB9-4ACF-B0DE-A8DA048F1AE5}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{05B7F7E9-1D94-4ED9-AC1A-6B89F40E219A}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{935201C6-B135-4930-883A-21C9F1FA5414}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W55</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{6D0ADB7B-20A8-4173-B45E-6CAFE79308CE}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>U2:U55</xm:sqref>
         </x14:dataValidation>
@@ -52643,135 +53024,135 @@
     <mergeCell ref="D53:F53"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:G34">
-    <cfRule type="expression" dxfId="141" priority="24">
+    <cfRule type="expression" dxfId="140" priority="24">
       <formula>$I2&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="25">
+    <cfRule type="expression" dxfId="139" priority="25">
       <formula>$I2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:L34 O2:P34">
-    <cfRule type="expression" dxfId="139" priority="22">
-      <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="138" priority="23">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
+    <cfRule type="expression" dxfId="137" priority="22">
+      <formula>AND(OR($I2="Addition",$I2="Omission"), H2="")</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:P34">
-    <cfRule type="expression" dxfId="137" priority="21">
+    <cfRule type="expression" dxfId="136" priority="21">
       <formula>AND(OR($I2="Addition",$I2="Omission"), H2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K34">
-    <cfRule type="expression" dxfId="136" priority="16">
+    <cfRule type="expression" dxfId="135" priority="16">
       <formula>AND($K2&lt;&gt;"",$K2&gt;1)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:N34">
-    <cfRule type="expression" dxfId="135" priority="12">
+    <cfRule type="expression" dxfId="134" priority="12">
       <formula>$N2="Absent"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="13">
+    <cfRule type="expression" dxfId="133" priority="13">
       <formula>$N2="NA"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="14">
+    <cfRule type="expression" dxfId="132" priority="14">
       <formula>AND(OR($I2="Addition",$I2="Omission"), M2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="132" priority="15">
+    <cfRule type="expression" dxfId="131" priority="15">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O34">
-    <cfRule type="expression" dxfId="131" priority="17">
+    <cfRule type="expression" dxfId="130" priority="17">
       <formula>AND(OR($I2="Addition",$I2="Omission",$I2="Substitution - Word"),RIGHT($AE2,6)&lt;&gt;"strict",$AD2&lt;&gt;"Yes")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q34">
-    <cfRule type="expression" dxfId="130" priority="2">
+    <cfRule type="expression" dxfId="129" priority="2">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="3">
+    <cfRule type="expression" dxfId="128" priority="3">
       <formula>AND(OR($I2="Addition",$I2="Omission"), Q2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="4">
+    <cfRule type="expression" dxfId="127" priority="4">
       <formula>AND($I2&lt;&gt;"Addition",$I2&lt;&gt;"Omission",$I2&lt;&gt;"Substitution - Word")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:T34">
-    <cfRule type="expression" dxfId="127" priority="18">
-      <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
+    <cfRule type="expression" dxfId="126" priority="20">
+      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="19">
+    <cfRule type="expression" dxfId="125" priority="19">
       <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="20">
-      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
+    <cfRule type="expression" dxfId="124" priority="18">
+      <formula>AND(AND(LEFT($I2,3)="Sub", RIGHT($I2,4)&lt;&gt;"Form"),$T2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S63:T63">
-    <cfRule type="expression" dxfId="124" priority="31">
+    <cfRule type="expression" dxfId="123" priority="33">
+      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="122" priority="31">
       <formula>AND(AND(LEFT($I63,3)="Sub", RIGHT($I63,4)&lt;&gt;"Form"),$T63&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="32">
+    <cfRule type="expression" dxfId="121" priority="32">
       <formula>AND(AND(LEFT($I63,3)="Sub", RIGHT($I63,4)&lt;&gt;"Form"),$T63="")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="122" priority="33">
-      <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S69:T69">
-    <cfRule type="expression" dxfId="121" priority="28">
+    <cfRule type="expression" dxfId="120" priority="28">
       <formula>AND(AND(LEFT($I69,3)="Sub", RIGHT($I69,4)&lt;&gt;"Form"),$T69&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="29">
+    <cfRule type="expression" dxfId="119" priority="29">
       <formula>AND(AND(LEFT($I69,3)="Sub", RIGHT($I69,4)&lt;&gt;"Form"),$T69="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="30">
+    <cfRule type="expression" dxfId="118" priority="30">
       <formula>"&lt;&gt;AND(LEFT($J2,3)=""Sub"", RIGHT($J2,4)&lt;&gt;""Form"")"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U34">
-    <cfRule type="expression" dxfId="118" priority="6">
-      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
-    </cfRule>
     <cfRule type="expression" dxfId="117" priority="7">
       <formula>OR($AD2="Yes",$AE2&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="10">
+    <cfRule type="expression" dxfId="116" priority="6">
+      <formula>AND($W2&lt;&gt;"",OR($AD2="Yes",$AE2&lt;&gt;""))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="115" priority="10">
       <formula>AND($AD2&lt;&gt;"Yes",$AE2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD12">
-    <cfRule type="expression" dxfId="115" priority="26">
+    <cfRule type="expression" dxfId="114" priority="26">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:AD34">
-    <cfRule type="expression" dxfId="114" priority="27">
+    <cfRule type="expression" dxfId="113" priority="27">
       <formula>OR($I2="",$I2="Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U13:AD34">
-    <cfRule type="expression" dxfId="113" priority="1">
+    <cfRule type="expression" dxfId="112" priority="1">
       <formula>AND($I13&lt;&gt;"",$I13&lt;&gt;"Unclear due to correction")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V34">
-    <cfRule type="expression" dxfId="112" priority="5">
+    <cfRule type="expression" dxfId="111" priority="5">
       <formula>AND($I2&lt;&gt;"",$I2&lt;&gt;"Unclear due to correction",$X2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W34">
-    <cfRule type="expression" dxfId="111" priority="8">
+    <cfRule type="expression" dxfId="110" priority="8">
       <formula>AND($X2="Yes",$Y2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="9">
+    <cfRule type="expression" dxfId="109" priority="9">
       <formula>$X2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB2:AB34">
-    <cfRule type="expression" dxfId="109" priority="11">
+    <cfRule type="expression" dxfId="108" priority="11">
       <formula>AND(OR($AB2&lt;&gt;"",$AC2&lt;&gt;""),$AD2="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52836,49 +53217,49 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" xr:uid="{0AC131B5-911D-46D1-A86E-BD21A081475C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$I$2:$I$1048576</xm:f>
+            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>V2:V34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BEE5C31C-1925-4A60-9FB5-B4F4133ACD79}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
+            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>X2:X34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D4525FA6-6588-4127-8E18-CD062B233E71}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$J$2:$J$1048576</xm:f>
+            <xm:f>'Data Regularization'!$K$2:$K$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>W2:W34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9A4D74D-9149-4A8C-AB17-1B38F0220497}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$L$2:$L$1048576</xm:f>
+            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Y2:Y34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2D4FE5D5-62D5-457D-AC6F-8B3399A26CE8}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$M$2:$M$1048576</xm:f>
+            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>Z2:Z34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3B4D364-8C86-4BC8-9E35-33E100F0B4E3}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
+            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AC2:AC34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8ED2541C-745A-4208-8B70-A89930419E7D}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$P$2:$P$1048576</xm:f>
+            <xm:f>'Data Regularization'!$Q$2:$Q$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AD2:AD34</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{47E53398-EE57-4ABD-97F1-AFA08061472C}">
           <x14:formula1>
-            <xm:f>'Data Regularization'!$N$2:$N$1048576</xm:f>
+            <xm:f>'Data Regularization'!$O$2:$O$1048576</xm:f>
           </x14:formula1>
           <xm:sqref>AB2:AB34</xm:sqref>
         </x14:dataValidation>
